--- a/results/Treatment_1994/synth_results_1994.xlsx
+++ b/results/Treatment_1994/synth_results_1994.xlsx
@@ -391,16 +391,16 @@
         <v>1950</v>
       </c>
       <c r="B2">
-        <v>0.0008904109589041096</v>
+        <v>0.0008925109307836388</v>
       </c>
       <c r="C2">
-        <v>0.000781561773732649</v>
+        <v>0.0007900821007009508</v>
       </c>
       <c r="D2">
-        <v>0.0001088491851714606</v>
+        <v>0.0001024288300826879</v>
       </c>
       <c r="E2">
-        <v>13.92713779380604</v>
+        <v>12.96432737709339</v>
       </c>
     </row>
     <row r="3">
@@ -408,16 +408,16 @@
         <v>1951</v>
       </c>
       <c r="B3">
-        <v>0.0005999999999999999</v>
+        <v>0.000601264402394389</v>
       </c>
       <c r="C3">
-        <v>0.0007525287339287782</v>
+        <v>0.0007576727673896568</v>
       </c>
       <c r="D3">
-        <v>-0.0001525287339287783</v>
+        <v>-0.0001564083649952679</v>
       </c>
       <c r="E3">
-        <v>-20.26882523574364</v>
+        <v>-20.64326074884911</v>
       </c>
     </row>
     <row r="4">
@@ -425,16 +425,16 @@
         <v>1952</v>
       </c>
       <c r="B4">
-        <v>0.0007808219178082191</v>
+        <v>0.0007846351628494586</v>
       </c>
       <c r="C4">
-        <v>0.0008579568696133458</v>
+        <v>0.0008599827763994324</v>
       </c>
       <c r="D4">
-        <v>-7.713495180512676E-05</v>
+        <v>-7.534761354997376E-05</v>
       </c>
       <c r="E4">
-        <v>-8.990539564056297</v>
+        <v>-8.761525883743674</v>
       </c>
     </row>
     <row r="5">
@@ -442,16 +442,16 @@
         <v>1953</v>
       </c>
       <c r="B5">
-        <v>0.0006705479452054794</v>
+        <v>0.0006722818491672769</v>
       </c>
       <c r="C5">
-        <v>0.0009692991768344536</v>
+        <v>0.0009797702793797498</v>
       </c>
       <c r="D5">
-        <v>-0.0002987512316289742</v>
+        <v>-0.0003074884302124729</v>
       </c>
       <c r="E5">
-        <v>-30.82136442172981</v>
+        <v>-31.38372705152176</v>
       </c>
     </row>
     <row r="6">
@@ -459,16 +459,16 @@
         <v>1954</v>
       </c>
       <c r="B6">
-        <v>0.0009657534246575343</v>
+        <v>0.000967773776393036</v>
       </c>
       <c r="C6">
-        <v>0.0007222223960021823</v>
+        <v>0.0007304784388951055</v>
       </c>
       <c r="D6">
-        <v>0.0002435310286553519</v>
+        <v>0.0002372953374979305</v>
       </c>
       <c r="E6">
-        <v>33.71967277716711</v>
+        <v>32.4849201376641</v>
       </c>
     </row>
     <row r="7">
@@ -476,16 +476,16 @@
         <v>1955</v>
       </c>
       <c r="B7">
-        <v>0.0008356164383561644</v>
+        <v>0.0008382239729680177</v>
       </c>
       <c r="C7">
-        <v>0.0006339456532503216</v>
+        <v>0.000637931013125676</v>
       </c>
       <c r="D7">
-        <v>0.0002016707851058428</v>
+        <v>0.0002002929598423417</v>
       </c>
       <c r="E7">
-        <v>31.81199903680237</v>
+        <v>31.39727583723585</v>
       </c>
     </row>
     <row r="8">
@@ -493,16 +493,16 @@
         <v>1956</v>
       </c>
       <c r="B8">
-        <v>0.0006438356164383561</v>
+        <v>0.0006449791045540373</v>
       </c>
       <c r="C8">
-        <v>0.0006371952542656979</v>
+        <v>0.0006513029618469804</v>
       </c>
       <c r="D8">
-        <v>6.640362172658214E-06</v>
+        <v>-6.323857292943151E-06</v>
       </c>
       <c r="E8">
-        <v>1.042123607827329</v>
+        <v>-0.9709547880773958</v>
       </c>
     </row>
     <row r="9">
@@ -510,16 +510,16 @@
         <v>1957</v>
       </c>
       <c r="B9">
-        <v>0.0008013698630136986</v>
+        <v>0.0008024510361586724</v>
       </c>
       <c r="C9">
-        <v>0.000643098057275934</v>
+        <v>0.0006536116367981857</v>
       </c>
       <c r="D9">
-        <v>0.0001582718057377646</v>
+        <v>0.0001488393993604867</v>
       </c>
       <c r="E9">
-        <v>24.61083561784963</v>
+        <v>22.77184049072302</v>
       </c>
     </row>
     <row r="10">
@@ -527,16 +527,16 @@
         <v>1958</v>
       </c>
       <c r="B10">
-        <v>0.0007876712328767123</v>
+        <v>0.0007880953588970963</v>
       </c>
       <c r="C10">
-        <v>0.0006720009511653645</v>
+        <v>0.0006768029134631385</v>
       </c>
       <c r="D10">
-        <v>0.0001156702817113477</v>
+        <v>0.0001112924454339579</v>
       </c>
       <c r="E10">
-        <v>17.21281517693624</v>
+        <v>16.44384845574683</v>
       </c>
     </row>
     <row r="11">
@@ -544,16 +544,16 @@
         <v>1959</v>
       </c>
       <c r="B11">
-        <v>0.0005897260273972603</v>
+        <v>0.0005910850529475994</v>
       </c>
       <c r="C11">
-        <v>0.0007530669918473661</v>
+        <v>0.0007553656717246537</v>
       </c>
       <c r="D11">
-        <v>-0.0001633409644501058</v>
+        <v>-0.0001642806187770543</v>
       </c>
       <c r="E11">
-        <v>-21.69009745725414</v>
+        <v>-21.74848883481403</v>
       </c>
     </row>
     <row r="12">
@@ -561,16 +561,16 @@
         <v>1960</v>
       </c>
       <c r="B12">
-        <v>0.0009041095890410959</v>
+        <v>0.0009027991600581399</v>
       </c>
       <c r="C12">
-        <v>0.0007494786504358783</v>
+        <v>0.0007533999749003519</v>
       </c>
       <c r="D12">
-        <v>0.0001546309386052176</v>
+        <v>0.000149399185157788</v>
       </c>
       <c r="E12">
-        <v>20.63180032083477</v>
+        <v>19.82999603597654</v>
       </c>
     </row>
     <row r="13">
@@ -578,16 +578,16 @@
         <v>1961</v>
       </c>
       <c r="B13">
-        <v>0.0004068493150684931</v>
+        <v>0.0004079966728743662</v>
       </c>
       <c r="C13">
-        <v>0.001662482826766993</v>
+        <v>0.001665219117341542</v>
       </c>
       <c r="D13">
-        <v>-0.0012556335116985</v>
+        <v>-0.001257222444467176</v>
       </c>
       <c r="E13">
-        <v>-75.52760795372021</v>
+        <v>-75.49891971419851</v>
       </c>
     </row>
     <row r="14">
@@ -595,16 +595,16 @@
         <v>1962</v>
       </c>
       <c r="B14">
-        <v>0.0008013698630136986</v>
+        <v>0.0008004313946064571</v>
       </c>
       <c r="C14">
-        <v>0.0009095143421611622</v>
+        <v>0.0009150180741652011</v>
       </c>
       <c r="D14">
-        <v>-0.0001081444791474636</v>
+        <v>-0.000114586679558744</v>
       </c>
       <c r="E14">
-        <v>-11.89035445999606</v>
+        <v>-12.52288701108827</v>
       </c>
     </row>
     <row r="15">
@@ -612,16 +612,16 @@
         <v>1963</v>
       </c>
       <c r="B15">
-        <v>0.0009863013698630137</v>
+        <v>0.000987215592526939</v>
       </c>
       <c r="C15">
-        <v>0.000808270729119363</v>
+        <v>0.0008054621423940838</v>
       </c>
       <c r="D15">
-        <v>0.0001780306407436507</v>
+        <v>0.0001817534501328552</v>
       </c>
       <c r="E15">
-        <v>22.02611505400187</v>
+        <v>22.5651139347937</v>
       </c>
     </row>
     <row r="16">
@@ -629,16 +629,16 @@
         <v>1964</v>
       </c>
       <c r="B16">
-        <v>0.0009315068493150684</v>
+        <v>0.0009362134403533977</v>
       </c>
       <c r="C16">
-        <v>0.0009110945031765543</v>
+        <v>0.0009077368502165943</v>
       </c>
       <c r="D16">
-        <v>2.041234613851404E-05</v>
+        <v>2.84765901368034E-05</v>
       </c>
       <c r="E16">
-        <v>2.240420293103062</v>
+        <v>3.137097511245536</v>
       </c>
     </row>
     <row r="17">
@@ -646,16 +646,16 @@
         <v>1965</v>
       </c>
       <c r="B17">
-        <v>0.0006465753424657534</v>
+        <v>0.0006482096531711096</v>
       </c>
       <c r="C17">
-        <v>0.0009710582930400352</v>
+        <v>0.0009717001973334813</v>
       </c>
       <c r="D17">
-        <v>-0.0003244829505742818</v>
+        <v>-0.0003234905441623717</v>
       </c>
       <c r="E17">
-        <v>-33.41539358656235</v>
+        <v>-33.29118848077704</v>
       </c>
     </row>
     <row r="18">
@@ -663,16 +663,16 @@
         <v>1966</v>
       </c>
       <c r="B18">
-        <v>0.0009246575342465753</v>
+        <v>0.0009283755558689517</v>
       </c>
       <c r="C18">
-        <v>0.0009914533619895089</v>
+        <v>0.0009928450737042805</v>
       </c>
       <c r="D18">
-        <v>-6.679582774293358E-05</v>
+        <v>-6.446951783532881E-05</v>
       </c>
       <c r="E18">
-        <v>-6.737162866531324</v>
+        <v>-6.49341166540663</v>
       </c>
     </row>
     <row r="19">
@@ -680,16 +680,16 @@
         <v>1967</v>
       </c>
       <c r="B19">
-        <v>0.0006917808219178081</v>
+        <v>0.0006951670355747701</v>
       </c>
       <c r="C19">
-        <v>0.001020795017970646</v>
+        <v>0.001019483421241641</v>
       </c>
       <c r="D19">
-        <v>-0.0003290141960528382</v>
+        <v>-0.0003243163856668707</v>
       </c>
       <c r="E19">
-        <v>-32.23117180831493</v>
+        <v>-31.81183518137862</v>
       </c>
     </row>
     <row r="20">
@@ -697,16 +697,16 @@
         <v>1968</v>
       </c>
       <c r="B20">
-        <v>0.001143835616438356</v>
+        <v>0.00114463838799432</v>
       </c>
       <c r="C20">
-        <v>0.00142698769068448</v>
+        <v>0.001404875542726291</v>
       </c>
       <c r="D20">
-        <v>-0.0002831520742461243</v>
+        <v>-0.0002602371547319707</v>
       </c>
       <c r="E20">
-        <v>-19.84264307916386</v>
+        <v>-18.52385829330878</v>
       </c>
     </row>
     <row r="21">
@@ -714,16 +714,16 @@
         <v>1969</v>
       </c>
       <c r="B21">
-        <v>0.000726027397260274</v>
+        <v>0.0007279888169643569</v>
       </c>
       <c r="C21">
-        <v>0.001203478124904056</v>
+        <v>0.001187482193860623</v>
       </c>
       <c r="D21">
-        <v>-0.0004774507276437816</v>
+        <v>-0.0004594933768962661</v>
       </c>
       <c r="E21">
-        <v>-39.67257216925694</v>
+        <v>-38.69475932118252</v>
       </c>
     </row>
     <row r="22">
@@ -731,16 +731,16 @@
         <v>1970</v>
       </c>
       <c r="B22">
-        <v>0.001465753424657534</v>
+        <v>0.001468158884709429</v>
       </c>
       <c r="C22">
-        <v>0.001563841842624712</v>
+        <v>0.001571856788253822</v>
       </c>
       <c r="D22">
-        <v>-9.808841796717809E-05</v>
+        <v>-0.0001036979035443928</v>
       </c>
       <c r="E22">
-        <v>-6.272272252451629</v>
+        <v>-6.597159761583046</v>
       </c>
     </row>
     <row r="23">
@@ -748,16 +748,16 @@
         <v>1971</v>
       </c>
       <c r="B23">
-        <v>0.0008561643835616438</v>
+        <v>0.0008588278038813216</v>
       </c>
       <c r="C23">
-        <v>0.001517174852680429</v>
+        <v>0.001518779196525473</v>
       </c>
       <c r="D23">
-        <v>-0.0006610104691187851</v>
+        <v>-0.000659951392644151</v>
       </c>
       <c r="E23">
-        <v>-43.56850945367056</v>
+        <v>-43.45275430121303</v>
       </c>
     </row>
     <row r="24">
@@ -765,16 +765,16 @@
         <v>1972</v>
       </c>
       <c r="B24">
-        <v>0.0007602739726027397</v>
+        <v>0.0007637643751805284</v>
       </c>
       <c r="C24">
-        <v>0.001400901554364732</v>
+        <v>0.001397010268441092</v>
       </c>
       <c r="D24">
-        <v>-0.0006406275817619919</v>
+        <v>-0.0006332458932605641</v>
       </c>
       <c r="E24">
-        <v>-45.72966456964908</v>
+        <v>-45.32864987221574</v>
       </c>
     </row>
     <row r="25">
@@ -782,16 +782,16 @@
         <v>1973</v>
       </c>
       <c r="B25">
-        <v>0.0007397260273972603</v>
+        <v>0.0007418358803387</v>
       </c>
       <c r="C25">
-        <v>0.001181190254653046</v>
+        <v>0.001174171729116041</v>
       </c>
       <c r="D25">
-        <v>-0.0004414642272557857</v>
+        <v>-0.0004323358487773413</v>
       </c>
       <c r="E25">
-        <v>-37.37452332651171</v>
+        <v>-36.82049550816722</v>
       </c>
     </row>
     <row r="26">
@@ -799,16 +799,16 @@
         <v>1974</v>
       </c>
       <c r="B26">
-        <v>0.0006917808219178081</v>
+        <v>0.0006960284420504502</v>
       </c>
       <c r="C26">
-        <v>0.001393734692938691</v>
+        <v>0.00138303906528535</v>
       </c>
       <c r="D26">
-        <v>-0.0007019538710208833</v>
+        <v>-0.0006870106232348996</v>
       </c>
       <c r="E26">
-        <v>-50.36495644237804</v>
+        <v>-49.67398539051064</v>
       </c>
     </row>
     <row r="27">
@@ -816,16 +816,16 @@
         <v>1975</v>
       </c>
       <c r="B27">
-        <v>0.001321917808219178</v>
+        <v>0.001324589309874286</v>
       </c>
       <c r="C27">
-        <v>0.00137791668530533</v>
+        <v>0.001370888385195199</v>
       </c>
       <c r="D27">
-        <v>-5.599887708615222E-05</v>
+        <v>-4.629907532091365E-05</v>
       </c>
       <c r="E27">
-        <v>-4.064024892313682</v>
+        <v>-3.377304514424139</v>
       </c>
     </row>
     <row r="28">
@@ -833,16 +833,16 @@
         <v>1976</v>
       </c>
       <c r="B28">
-        <v>0.0009657534246575343</v>
+        <v>0.000966460634461957</v>
       </c>
       <c r="C28">
-        <v>0.001921716660257753</v>
+        <v>0.001971011078259037</v>
       </c>
       <c r="D28">
-        <v>-0.0009559632356002183</v>
+        <v>-0.00100455044379708</v>
       </c>
       <c r="E28">
-        <v>-49.74527490811255</v>
+        <v>-50.9662505136391</v>
       </c>
     </row>
     <row r="29">
@@ -850,16 +850,16 @@
         <v>1977</v>
       </c>
       <c r="B29">
-        <v>0.0006061643835616438</v>
+        <v>0.0006072604742501553</v>
       </c>
       <c r="C29">
-        <v>0.001577311023543799</v>
+        <v>0.001582178464617161</v>
       </c>
       <c r="D29">
-        <v>-0.0009711466399821551</v>
+        <v>-0.0009749179903670055</v>
       </c>
       <c r="E29">
-        <v>-61.56976179626555</v>
+        <v>-61.61871193227915</v>
       </c>
     </row>
     <row r="30">
@@ -867,16 +867,16 @@
         <v>1978</v>
       </c>
       <c r="B30">
-        <v>0.001698630136986301</v>
+        <v>0.00170425790228867</v>
       </c>
       <c r="C30">
-        <v>0.001169269880035043</v>
+        <v>0.001158672521330521</v>
       </c>
       <c r="D30">
-        <v>0.0005293602569512584</v>
+        <v>0.000545585380958149</v>
       </c>
       <c r="E30">
-        <v>45.272718128632</v>
+        <v>47.0871079545103</v>
       </c>
     </row>
     <row r="31">
@@ -884,16 +884,16 @@
         <v>1979</v>
       </c>
       <c r="B31">
-        <v>0.000545890410958904</v>
+        <v>0.0005472440355566978</v>
       </c>
       <c r="C31">
-        <v>0.001901279436058903</v>
+        <v>0.001896169365590405</v>
       </c>
       <c r="D31">
-        <v>-0.0013553890251</v>
+        <v>-0.001348925330033708</v>
       </c>
       <c r="E31">
-        <v>-71.2882598630288</v>
+        <v>-71.13949600244155</v>
       </c>
     </row>
     <row r="32">
@@ -901,16 +901,16 @@
         <v>1980</v>
       </c>
       <c r="B32">
-        <v>0.0008013698630136986</v>
+        <v>0.0008034864918550222</v>
       </c>
       <c r="C32">
-        <v>0.001328365199443271</v>
+        <v>0.001320830971187189</v>
       </c>
       <c r="D32">
-        <v>-0.0005269953364295723</v>
+        <v>-0.0005173444793321669</v>
       </c>
       <c r="E32">
-        <v>-39.67247385360897</v>
+        <v>-39.16810633741935</v>
       </c>
     </row>
     <row r="33">
@@ -918,16 +918,16 @@
         <v>1981</v>
       </c>
       <c r="B33">
-        <v>0.0009657534246575343</v>
+        <v>0.0009658822789605574</v>
       </c>
       <c r="C33">
-        <v>0.001280175285205823</v>
+        <v>0.001281754463631941</v>
       </c>
       <c r="D33">
-        <v>-0.000314421860548289</v>
+        <v>-0.0003158721846713836</v>
       </c>
       <c r="E33">
-        <v>-24.56084445480738</v>
+        <v>-24.64373588185819</v>
       </c>
     </row>
     <row r="34">
@@ -935,16 +935,16 @@
         <v>1982</v>
       </c>
       <c r="B34">
-        <v>0.0009246575342465753</v>
+        <v>0.0009285557013845663</v>
       </c>
       <c r="C34">
-        <v>0.001656520736512632</v>
+        <v>0.001672974741037889</v>
       </c>
       <c r="D34">
-        <v>-0.0007318632022660569</v>
+        <v>-0.0007444190396533224</v>
       </c>
       <c r="E34">
-        <v>-44.18074498764211</v>
+        <v>-44.49672917305947</v>
       </c>
     </row>
     <row r="35">
@@ -952,16 +952,16 @@
         <v>1983</v>
       </c>
       <c r="B35">
-        <v>0.00113013698630137</v>
+        <v>0.001135396282932322</v>
       </c>
       <c r="C35">
-        <v>0.001799917155681238</v>
+        <v>0.001806565913878563</v>
       </c>
       <c r="D35">
-        <v>-0.0006697801693798682</v>
+        <v>-0.0006711696309462409</v>
       </c>
       <c r="E35">
-        <v>-37.21172206541738</v>
+        <v>-37.15168241524548</v>
       </c>
     </row>
     <row r="36">
@@ -969,16 +969,16 @@
         <v>1984</v>
       </c>
       <c r="B36">
-        <v>0.001198630136986301</v>
+        <v>0.001203020044235418</v>
       </c>
       <c r="C36">
-        <v>0.001611313817412102</v>
+        <v>0.001614702497967007</v>
       </c>
       <c r="D36">
-        <v>-0.000412683680425801</v>
+        <v>-0.0004116824537315888</v>
       </c>
       <c r="E36">
-        <v>-25.61162673380433</v>
+        <v>-25.49587024544261</v>
       </c>
     </row>
     <row r="37">
@@ -986,16 +986,16 @@
         <v>1985</v>
       </c>
       <c r="B37">
-        <v>0.001636986301369863</v>
+        <v>0.001642536207973294</v>
       </c>
       <c r="C37">
-        <v>0.001702481002721855</v>
+        <v>0.001720527054641184</v>
       </c>
       <c r="D37">
-        <v>-6.549470135199203E-05</v>
+        <v>-7.79908466678901E-05</v>
       </c>
       <c r="E37">
-        <v>-3.847015106029487</v>
+        <v>-4.532962527820007</v>
       </c>
     </row>
     <row r="38">
@@ -1003,16 +1003,16 @@
         <v>1986</v>
       </c>
       <c r="B38">
-        <v>0.002801369863013698</v>
+        <v>0.002803928189882721</v>
       </c>
       <c r="C38">
-        <v>0.002028307469595692</v>
+        <v>0.002068193916732271</v>
       </c>
       <c r="D38">
-        <v>0.0007730623934180062</v>
+        <v>0.0007357342731504506</v>
       </c>
       <c r="E38">
-        <v>38.11366890898956</v>
+        <v>35.57375675453609</v>
       </c>
     </row>
     <row r="39">
@@ -1020,16 +1020,16 @@
         <v>1987</v>
       </c>
       <c r="B39">
-        <v>0.004417808219178082</v>
+        <v>0.004427640502177702</v>
       </c>
       <c r="C39">
-        <v>0.002245944286679796</v>
+        <v>0.002258997292687266</v>
       </c>
       <c r="D39">
-        <v>0.002171863932498287</v>
+        <v>0.002168643209490436</v>
       </c>
       <c r="E39">
-        <v>96.70159430842239</v>
+        <v>96.00025712782742</v>
       </c>
     </row>
     <row r="40">
@@ -1037,16 +1037,16 @@
         <v>1988</v>
       </c>
       <c r="B40">
-        <v>0.002767123287671233</v>
+        <v>0.002771119637453164</v>
       </c>
       <c r="C40">
-        <v>0.002156660999228031</v>
+        <v>0.002161963082090652</v>
       </c>
       <c r="D40">
-        <v>0.0006104622884432012</v>
+        <v>0.0006091565553625116</v>
       </c>
       <c r="E40">
-        <v>28.30589919610517</v>
+        <v>28.17608498538502</v>
       </c>
     </row>
     <row r="41">
@@ -1054,16 +1054,16 @@
         <v>1989</v>
       </c>
       <c r="B41">
-        <v>0.002582191780821918</v>
+        <v>0.00258858437422026</v>
       </c>
       <c r="C41">
-        <v>0.002206035210051533</v>
+        <v>0.002218049823015275</v>
       </c>
       <c r="D41">
-        <v>0.0003761565707703844</v>
+        <v>0.0003705345512049854</v>
       </c>
       <c r="E41">
-        <v>17.05124963810515</v>
+        <v>16.70542056180104</v>
       </c>
     </row>
     <row r="42">
@@ -1071,16 +1071,16 @@
         <v>1990</v>
       </c>
       <c r="B42">
-        <v>0.002404109589041096</v>
+        <v>0.002405775996973834</v>
       </c>
       <c r="C42">
-        <v>0.002255815326132055</v>
+        <v>0.002256699978126454</v>
       </c>
       <c r="D42">
-        <v>0.0001482942629090407</v>
+        <v>0.00014907601884738</v>
       </c>
       <c r="E42">
-        <v>6.573865386548026</v>
+        <v>6.605929910592062</v>
       </c>
     </row>
     <row r="43">
@@ -1088,16 +1088,16 @@
         <v>1991</v>
       </c>
       <c r="B43">
-        <v>0.002349315068493151</v>
+        <v>0.002350898856844621</v>
       </c>
       <c r="C43">
-        <v>0.002307908331989717</v>
+        <v>0.002301727221906746</v>
       </c>
       <c r="D43">
-        <v>4.140673650343324E-05</v>
+        <v>4.917163493787504E-05</v>
       </c>
       <c r="E43">
-        <v>1.79412396625542</v>
+        <v>2.13629288778804</v>
       </c>
     </row>
     <row r="44">
@@ -1105,16 +1105,16 @@
         <v>1992</v>
       </c>
       <c r="B44">
-        <v>0.003664383561643835</v>
+        <v>0.003673850458044975</v>
       </c>
       <c r="C44">
-        <v>0.003069004787742351</v>
+        <v>0.003047053564615695</v>
       </c>
       <c r="D44">
-        <v>0.0005953787739014843</v>
+        <v>0.0006267968934292796</v>
       </c>
       <c r="E44">
-        <v>19.39973428127045</v>
+        <v>20.57058992030989</v>
       </c>
     </row>
     <row r="45">
@@ -1122,16 +1122,16 @@
         <v>1993</v>
       </c>
       <c r="B45">
-        <v>0.00363013698630137</v>
+        <v>0.003637478255442569</v>
       </c>
       <c r="C45">
-        <v>0.00269923518436367</v>
+        <v>0.002688093155111806</v>
       </c>
       <c r="D45">
-        <v>0.0009309018019376994</v>
+        <v>0.0009493851003307637</v>
       </c>
       <c r="E45">
-        <v>34.48761365183354</v>
+        <v>35.31816218963126</v>
       </c>
     </row>
     <row r="46">
@@ -1139,16 +1139,16 @@
         <v>1994</v>
       </c>
       <c r="B46">
-        <v>0.004164383561643835</v>
+        <v>0.004170422211947586</v>
       </c>
       <c r="C46">
-        <v>0.00263512830592769</v>
+        <v>0.002643214327013855</v>
       </c>
       <c r="D46">
-        <v>0.001529255255716145</v>
+        <v>0.001527207884933731</v>
       </c>
       <c r="E46">
-        <v>58.03342677000217</v>
+        <v>57.77843549520551</v>
       </c>
     </row>
     <row r="47">
@@ -1156,16 +1156,16 @@
         <v>1995</v>
       </c>
       <c r="B47">
-        <v>0.003835616438356164</v>
+        <v>0.00384678356903645</v>
       </c>
       <c r="C47">
-        <v>0.002477690197327138</v>
+        <v>0.002463195389376362</v>
       </c>
       <c r="D47">
-        <v>0.001357926241029026</v>
+        <v>0.001383588179660088</v>
       </c>
       <c r="E47">
-        <v>54.80613526638314</v>
+        <v>56.17045994919584</v>
       </c>
     </row>
     <row r="48">
@@ -1173,16 +1173,16 @@
         <v>1996</v>
       </c>
       <c r="B48">
-        <v>0.006746575342465753</v>
+        <v>0.006757800495175996</v>
       </c>
       <c r="C48">
-        <v>0.003290780137758894</v>
+        <v>0.003274241922999217</v>
       </c>
       <c r="D48">
-        <v>0.003455795204706859</v>
+        <v>0.003483558572176779</v>
       </c>
       <c r="E48">
-        <v>105.0144664802901</v>
+        <v>106.39282783924</v>
       </c>
     </row>
     <row r="49">
@@ -1190,16 +1190,16 @@
         <v>1997</v>
       </c>
       <c r="B49">
-        <v>0.006054794520547945</v>
+        <v>0.006066215825399553</v>
       </c>
       <c r="C49">
-        <v>0.003089343025771532</v>
+        <v>0.00306151410775141</v>
       </c>
       <c r="D49">
-        <v>0.002965451494776413</v>
+        <v>0.003004701717648143</v>
       </c>
       <c r="E49">
-        <v>95.98971270067432</v>
+        <v>98.14430415461997</v>
       </c>
     </row>
     <row r="50">
@@ -1207,16 +1207,16 @@
         <v>1998</v>
       </c>
       <c r="B50">
-        <v>0.006020547945205479</v>
+        <v>0.006030570057302754</v>
       </c>
       <c r="C50">
-        <v>0.002893729970425057</v>
+        <v>0.002866457527992491</v>
       </c>
       <c r="D50">
-        <v>0.003126817974780422</v>
+        <v>0.003164112529310263</v>
       </c>
       <c r="E50">
-        <v>108.0549327939237</v>
+        <v>110.3840715730483</v>
       </c>
     </row>
     <row r="51">
@@ -1224,16 +1224,16 @@
         <v>1999</v>
       </c>
       <c r="B51">
-        <v>0.009383561643835615</v>
+        <v>0.009398582809823192</v>
       </c>
       <c r="C51">
-        <v>0.002945166272061876</v>
+        <v>0.002907990527644318</v>
       </c>
       <c r="D51">
-        <v>0.00643839537177374</v>
+        <v>0.006490592282178874</v>
       </c>
       <c r="E51">
-        <v>218.6088925725167</v>
+        <v>223.1985359125885</v>
       </c>
     </row>
     <row r="52">
@@ -1241,16 +1241,16 @@
         <v>2000</v>
       </c>
       <c r="B52">
-        <v>0.006698630136986301</v>
+        <v>0.006715401495391304</v>
       </c>
       <c r="C52">
-        <v>0.003294245269030883</v>
+        <v>0.003270465543345089</v>
       </c>
       <c r="D52">
-        <v>0.003404384867955418</v>
+        <v>0.003444935952046215</v>
       </c>
       <c r="E52">
-        <v>103.3433940077247</v>
+        <v>105.3347270102309</v>
       </c>
     </row>
     <row r="53">
@@ -1258,16 +1258,16 @@
         <v>2001</v>
       </c>
       <c r="B53">
-        <v>0.006294520547945204</v>
+        <v>0.006311136669467308</v>
       </c>
       <c r="C53">
-        <v>0.003239510339409145</v>
+        <v>0.003214392351603626</v>
       </c>
       <c r="D53">
-        <v>0.003055010208536059</v>
+        <v>0.003096744317863682</v>
       </c>
       <c r="E53">
-        <v>94.30469078525194</v>
+        <v>96.33996037598673</v>
       </c>
     </row>
     <row r="54">
@@ -1275,16 +1275,16 @@
         <v>2002</v>
       </c>
       <c r="B54">
-        <v>0.006815068493150684</v>
+        <v>0.006831282795920907</v>
       </c>
       <c r="C54">
-        <v>0.003657448994137793</v>
+        <v>0.003649215924462094</v>
       </c>
       <c r="D54">
-        <v>0.003157619499012891</v>
+        <v>0.003182066871458813</v>
       </c>
       <c r="E54">
-        <v>86.33393122020196</v>
+        <v>87.19864588248119</v>
       </c>
     </row>
     <row r="55">
@@ -1292,16 +1292,16 @@
         <v>2003</v>
       </c>
       <c r="B55">
-        <v>0.006917808219178082</v>
+        <v>0.006946805634307765</v>
       </c>
       <c r="C55">
-        <v>0.003664866439988443</v>
+        <v>0.003627778450573806</v>
       </c>
       <c r="D55">
-        <v>0.003252941779189639</v>
+        <v>0.003319027183733958</v>
       </c>
       <c r="E55">
-        <v>88.76017264083154</v>
+        <v>91.48924690285281</v>
       </c>
     </row>
     <row r="56">
@@ -1309,16 +1309,16 @@
         <v>2004</v>
       </c>
       <c r="B56">
-        <v>0.008904109589041096</v>
+        <v>0.008921179514189163</v>
       </c>
       <c r="C56">
-        <v>0.003342609506818348</v>
+        <v>0.003326113267619646</v>
       </c>
       <c r="D56">
-        <v>0.005561500082222748</v>
+        <v>0.005595066246569518</v>
       </c>
       <c r="E56">
-        <v>166.3819860165612</v>
+        <v>168.2163473216191</v>
       </c>
     </row>
     <row r="57">
@@ -1326,16 +1326,16 @@
         <v>2005</v>
       </c>
       <c r="B57">
-        <v>0.008150684931506849</v>
+        <v>0.008166187524545149</v>
       </c>
       <c r="C57">
-        <v>0.003213542014732494</v>
+        <v>0.003197251540479878</v>
       </c>
       <c r="D57">
-        <v>0.004937142916774355</v>
+        <v>0.004968935984065271</v>
       </c>
       <c r="E57">
-        <v>153.6355490029384</v>
+        <v>155.4127325033513</v>
       </c>
     </row>
     <row r="58">
@@ -1343,16 +1343,16 @@
         <v>2006</v>
       </c>
       <c r="B58">
-        <v>0.009452054794520546</v>
+        <v>0.00949555876817402</v>
       </c>
       <c r="C58">
-        <v>0.003353622713787582</v>
+        <v>0.003329091122692848</v>
       </c>
       <c r="D58">
-        <v>0.006098432080732965</v>
+        <v>0.006166467645481172</v>
       </c>
       <c r="E58">
-        <v>181.8460990158727</v>
+        <v>185.2297644677631</v>
       </c>
     </row>
     <row r="59">
@@ -1360,16 +1360,16 @@
         <v>2007</v>
       </c>
       <c r="B59">
-        <v>0.01438356164383562</v>
+        <v>0.01441355012104101</v>
       </c>
       <c r="C59">
-        <v>0.004690925603020786</v>
+        <v>0.004757670159622293</v>
       </c>
       <c r="D59">
-        <v>0.00969263604081483</v>
+        <v>0.00965587996141872</v>
       </c>
       <c r="E59">
-        <v>206.6252347846473</v>
+        <v>202.9539593426815</v>
       </c>
     </row>
     <row r="60">
@@ -1377,16 +1377,16 @@
         <v>2008</v>
       </c>
       <c r="B60">
-        <v>0.01232876712328767</v>
+        <v>0.01234909494853939</v>
       </c>
       <c r="C60">
-        <v>0.003213710356155527</v>
+        <v>0.00319599883271274</v>
       </c>
       <c r="D60">
-        <v>0.009115056767132144</v>
+        <v>0.00915309611582665</v>
       </c>
       <c r="E60">
-        <v>283.6303137796224</v>
+        <v>286.3923485246573</v>
       </c>
     </row>
     <row r="61">
@@ -1394,16 +1394,16 @@
         <v>2009</v>
       </c>
       <c r="B61">
-        <v>0.01589041095890411</v>
+        <v>0.01590268282080393</v>
       </c>
       <c r="C61">
-        <v>0.003839965812771343</v>
+        <v>0.003820053611720307</v>
       </c>
       <c r="D61">
-        <v>0.01205044514613277</v>
+        <v>0.01208262920908363</v>
       </c>
       <c r="E61">
-        <v>313.8164695647598</v>
+        <v>316.2947549221013</v>
       </c>
     </row>
     <row r="62">
@@ -1411,16 +1411,16 @@
         <v>2010</v>
       </c>
       <c r="B62">
-        <v>0.01280821917808219</v>
+        <v>0.01286010102190836</v>
       </c>
       <c r="C62">
-        <v>0.003612891033538215</v>
+        <v>0.003590624940386215</v>
       </c>
       <c r="D62">
-        <v>0.009195328144543977</v>
+        <v>0.009269476081522147</v>
       </c>
       <c r="E62">
-        <v>254.5144057538517</v>
+        <v>258.1577367566857</v>
       </c>
     </row>
     <row r="63">
@@ -1428,16 +1428,16 @@
         <v>2011</v>
       </c>
       <c r="B63">
-        <v>0.01328767123287671</v>
+        <v>0.013317830354497</v>
       </c>
       <c r="C63">
-        <v>0.003301020925300026</v>
+        <v>0.003283421415596607</v>
       </c>
       <c r="D63">
-        <v>0.009986650307576684</v>
+        <v>0.01003440893890039</v>
       </c>
       <c r="E63">
-        <v>302.5321721239622</v>
+        <v>305.6083173252102</v>
       </c>
     </row>
     <row r="64">
@@ -1445,16 +1445,16 @@
         <v>2012</v>
       </c>
       <c r="B64">
-        <v>0.01287671232876712</v>
+        <v>0.01288385608864151</v>
       </c>
       <c r="C64">
-        <v>0.003162957623759401</v>
+        <v>0.003159183170027751</v>
       </c>
       <c r="D64">
-        <v>0.00971375470500772</v>
+        <v>0.009724672918613762</v>
       </c>
       <c r="E64">
-        <v>307.109859203938</v>
+        <v>307.8223830411308</v>
       </c>
     </row>
     <row r="65">
@@ -1462,16 +1462,16 @@
         <v>2013</v>
       </c>
       <c r="B65">
-        <v>0.01883561643835616</v>
+        <v>0.01884221187454784</v>
       </c>
       <c r="C65">
-        <v>0.00419981678881</v>
+        <v>0.00419014379431986</v>
       </c>
       <c r="D65">
-        <v>0.01463579964954616</v>
+        <v>0.01465206808022798</v>
       </c>
       <c r="E65">
-        <v>348.4866218103088</v>
+        <v>349.6793618417168</v>
       </c>
     </row>
     <row r="66">
@@ -1479,16 +1479,16 @@
         <v>2014</v>
       </c>
       <c r="B66">
-        <v>0.01397260273972603</v>
+        <v>0.01400822649061103</v>
       </c>
       <c r="C66">
-        <v>0.004380455493852716</v>
+        <v>0.004380573662051698</v>
       </c>
       <c r="D66">
-        <v>0.00959214724587331</v>
+        <v>0.009627652828559329</v>
       </c>
       <c r="E66">
-        <v>218.9760233686745</v>
+        <v>219.7806399641752</v>
       </c>
     </row>
     <row r="67">
@@ -1496,16 +1496,16 @@
         <v>2015</v>
       </c>
       <c r="B67">
-        <v>0.0210958904109589</v>
+        <v>0.02115557925734338</v>
       </c>
       <c r="C67">
-        <v>0.004415240388031986</v>
+        <v>0.004393542278542851</v>
       </c>
       <c r="D67">
-        <v>0.01668065002292692</v>
+        <v>0.01676203697880053</v>
       </c>
       <c r="E67">
-        <v>377.7970972575294</v>
+        <v>381.515322173246</v>
       </c>
     </row>
     <row r="68">
@@ -1513,16 +1513,16 @@
         <v>2016</v>
       </c>
       <c r="B68">
-        <v>0.02575342465753424</v>
+        <v>0.02577512137030696</v>
       </c>
       <c r="C68">
-        <v>0.005304876160943427</v>
+        <v>0.005309556607796311</v>
       </c>
       <c r="D68">
-        <v>0.02044854849659081</v>
+        <v>0.02046556476251065</v>
       </c>
       <c r="E68">
-        <v>385.4670283755354</v>
+        <v>385.4477176580045</v>
       </c>
     </row>
   </sheetData>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.7918885489025389</v>
+        <v>0.7984732484102118</v>
       </c>
     </row>
     <row r="3">
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.1533131232602718</v>
+        <v>0.1463443373495891</v>
       </c>
     </row>
     <row r="4">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.03697862982845249</v>
+        <v>0.03656503409667033</v>
       </c>
     </row>
     <row r="5">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.01060464753981749</v>
+        <v>0.01205217265148442</v>
       </c>
     </row>
     <row r="6">
@@ -1594,337 +1594,337 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.004193344589848595</v>
+        <v>0.004018471904724649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Arthur Moeller van den Bruck</t>
+          <t>Julius Evola</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.0006452316227192612</v>
+        <v>0.0002687846454937457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Julius Evola</t>
+          <t>Oswald Spengler</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.0003698019290251515</v>
+        <v>0.000213313503707758</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Oswald Spengler</t>
+          <t>Ferdinand Tönnies</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.0001725637916435429</v>
+        <v>9.328801776610382E-05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Schäffle</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.0001008355905203865</v>
+        <v>7.962804454693558E-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ferdinand Tönnies</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B11">
-        <v>8.817209085819821E-05</v>
+        <v>7.884683531562844E-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Descartes</t>
+          <t>Hobbes</t>
         </is>
       </c>
       <c r="B12">
-        <v>7.19829389425392E-05</v>
+        <v>6.216005955958785E-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Schäffle</t>
+          <t>Friedrich List</t>
         </is>
       </c>
       <c r="B13">
-        <v>7.127277994507211E-05</v>
+        <v>4.292963597223905E-05</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tocqueville</t>
+          <t>Descartes</t>
         </is>
       </c>
       <c r="B14">
-        <v>6.094332035975266E-05</v>
+        <v>4.134232449948677E-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hobbes</t>
+          <t>Ferdinand Lassalle</t>
         </is>
       </c>
       <c r="B15">
-        <v>5.935881438745341E-05</v>
+        <v>3.772100714024106E-05</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Friedrich List</t>
+          <t>Tocqueville</t>
         </is>
       </c>
       <c r="B16">
-        <v>4.394477537737512E-05</v>
+        <v>3.487534785898618E-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Gaetano Mosca</t>
+          <t>Eduard Bernstein</t>
         </is>
       </c>
       <c r="B17">
-        <v>3.864298641298851E-05</v>
+        <v>3.471552186643922E-05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>de Gouges</t>
+          <t>August Bebel</t>
         </is>
       </c>
       <c r="B18">
-        <v>3.707425875661502E-05</v>
+        <v>3.413453833721208E-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Aquinas</t>
+          <t>de Gouges</t>
         </is>
       </c>
       <c r="B19">
-        <v>3.374480029911349E-05</v>
+        <v>3.341283039105016E-05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ferdinand Lassalle</t>
+          <t>Hans Kelsen</t>
         </is>
       </c>
       <c r="B20">
-        <v>3.170341025467063E-05</v>
+        <v>3.241584292615641E-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Eduard Bernstein</t>
+          <t>John C Calhoun</t>
         </is>
       </c>
       <c r="B21">
-        <v>3.060231530004808E-05</v>
+        <v>2.960375067629626E-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Augustine</t>
+          <t>Lujo Brentano</t>
         </is>
       </c>
       <c r="B22">
-        <v>2.912142956955193E-05</v>
+        <v>2.909322213666165E-05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Auberon Herbert</t>
         </is>
       </c>
       <c r="B23">
-        <v>2.863035906983395E-05</v>
+        <v>2.899316550929832E-05</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>August Bebel</t>
+          <t>Rodbertus</t>
         </is>
       </c>
       <c r="B24">
-        <v>2.749943455147537E-05</v>
+        <v>2.798649793007178E-05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rodbertus</t>
+          <t>Quentin Skinner</t>
         </is>
       </c>
       <c r="B25">
-        <v>2.512503772463857E-05</v>
+        <v>2.765110357219471E-05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Wilhelm von Humboldt</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
       <c r="B26">
-        <v>2.421232585324675E-05</v>
+        <v>2.753891268068245E-05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vilfredo Pareto</t>
+          <t>Gaetano Mosca</t>
         </is>
       </c>
       <c r="B27">
-        <v>2.361799860901487E-05</v>
+        <v>2.749155762829254E-05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Schmoller</t>
+          <t>Augustine</t>
         </is>
       </c>
       <c r="B28">
-        <v>2.022514383318331E-05</v>
+        <v>2.602559181803534E-05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Adam Smith</t>
+          <t>Wilhelm von Humboldt</t>
         </is>
       </c>
       <c r="B29">
-        <v>1.847881145153256E-05</v>
+        <v>2.538831442926373E-05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Blanqui</t>
+          <t>Aquinas</t>
         </is>
       </c>
       <c r="B30">
-        <v>1.711268716196071E-05</v>
+        <v>2.429174387888113E-05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Charles Fourier</t>
+          <t>Leo Strauss</t>
         </is>
       </c>
       <c r="B31">
-        <v>1.673166896593875E-05</v>
+        <v>2.398276288433366E-05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>James Fitzjames Stephen</t>
         </is>
       </c>
       <c r="B32">
-        <v>1.664245918149522E-05</v>
+        <v>2.085217243665471E-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>John C Calhoun</t>
+          <t>Adam Smith</t>
         </is>
       </c>
       <c r="B33">
-        <v>1.624159796434493E-05</v>
+        <v>1.929676254969776E-05</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lujo Brentano</t>
+          <t>Schmoller</t>
         </is>
       </c>
       <c r="B34">
-        <v>1.598588619884431E-05</v>
+        <v>1.855570562911542E-05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Auberon Herbert</t>
+          <t>Robert Nozick</t>
         </is>
       </c>
       <c r="B35">
-        <v>1.585436472494308E-05</v>
+        <v>1.773489650473964E-05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machiavelli</t>
+          <t>Arthur Moeller van den Bruck</t>
         </is>
       </c>
       <c r="B36">
-        <v>1.538995509681577E-05</v>
+        <v>1.745397732259846E-05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Benjamin Constant</t>
+          <t>Vilfredo Pareto</t>
         </is>
       </c>
       <c r="B37">
-        <v>1.475011578959382E-05</v>
+        <v>1.742092125054522E-05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sombart</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="B38">
-        <v>1.45805049153423E-05</v>
+        <v>1.71783438323988E-05</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quentin Skinner</t>
+          <t>Malthus</t>
         </is>
       </c>
       <c r="B39">
-        <v>1.434160620088462E-05</v>
+        <v>1.574583710315195E-05</v>
       </c>
     </row>
     <row r="40">
@@ -1934,507 +1934,507 @@
         </is>
       </c>
       <c r="B40">
-        <v>1.415651473739803E-05</v>
+        <v>1.566479815067236E-05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Malthus</t>
+          <t>Nassau Senior</t>
         </is>
       </c>
       <c r="B41">
-        <v>1.410402994678077E-05</v>
+        <v>1.531938924287759E-05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Spinoza</t>
+          <t>Charles Fourier</t>
         </is>
       </c>
       <c r="B42">
-        <v>1.3886153132859E-05</v>
+        <v>1.435065897377887E-05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thucydides</t>
+          <t>Machiavelli</t>
         </is>
       </c>
       <c r="B43">
-        <v>1.366454120462301E-05</v>
+        <v>1.40754237002232E-05</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Hans Kelsen</t>
+          <t>Bentham</t>
         </is>
       </c>
       <c r="B44">
-        <v>1.363040467880443E-05</v>
+        <v>1.39428658371675E-05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bastiat</t>
+          <t>Sombart</t>
         </is>
       </c>
       <c r="B45">
-        <v>1.349442480602527E-05</v>
+        <v>1.370493440425882E-05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Rousseau</t>
+          <t>Thucydides</t>
         </is>
       </c>
       <c r="B46">
-        <v>1.30473099942243E-05</v>
+        <v>1.359278211886464E-05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Plutarch</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="B47">
-        <v>1.30196451508973E-05</v>
+        <v>1.326545288705382E-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bentham</t>
+          <t>Plutarch</t>
         </is>
       </c>
       <c r="B48">
-        <v>1.273907416034312E-05</v>
+        <v>1.32479251051498E-05</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Alexander Hamilton</t>
         </is>
       </c>
       <c r="B49">
-        <v>1.229496605213217E-05</v>
+        <v>1.31302078917058E-05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alexander Hamilton</t>
+          <t>Spinoza</t>
         </is>
       </c>
       <c r="B50">
-        <v>1.175014357740525E-05</v>
+        <v>1.293574711471256E-05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hume</t>
+          <t>Oscar Wilde</t>
         </is>
       </c>
       <c r="B51">
-        <v>1.152363975349492E-05</v>
+        <v>1.261428234260754E-05</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Rousseau</t>
         </is>
       </c>
       <c r="B52">
-        <v>1.130301484646888E-05</v>
+        <v>1.224995110756734E-05</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>James Fitzjames Stephen</t>
+          <t>Hume</t>
         </is>
       </c>
       <c r="B53">
-        <v>1.128202938303704E-05</v>
+        <v>1.181592493562684E-05</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Pericles</t>
+          <t>Bastiat</t>
         </is>
       </c>
       <c r="B54">
-        <v>1.114600487914662E-05</v>
+        <v>1.174653349542714E-05</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Raymond Aron</t>
+          <t>William Penn</t>
         </is>
       </c>
       <c r="B55">
-        <v>1.097531979132618E-05</v>
+        <v>1.166192946410381E-05</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Chaucer</t>
+          <t>Pericles</t>
         </is>
       </c>
       <c r="B56">
-        <v>1.082830571470546E-05</v>
+        <v>1.155719362569891E-05</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oscar Wilde</t>
+          <t>Oliver Wendell Holmes</t>
         </is>
       </c>
       <c r="B57">
-        <v>1.079302389295313E-05</v>
+        <v>1.150867560290539E-05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Thomas More</t>
+          <t>Chaucer</t>
         </is>
       </c>
       <c r="B58">
-        <v>1.06555569717509E-05</v>
+        <v>1.146057975269106E-05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Leibniz</t>
+          <t>Carl Friedrich</t>
         </is>
       </c>
       <c r="B59">
-        <v>1.010495784741572E-05</v>
+        <v>1.1354321003812E-05</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="B60">
-        <v>9.99630826756507E-06</v>
+        <v>1.134727987213309E-05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>Blanqui</t>
         </is>
       </c>
       <c r="B61">
-        <v>9.981176486590741E-06</v>
+        <v>1.133312863302561E-05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>William Penn</t>
+          <t>Benjamin Constant</t>
         </is>
       </c>
       <c r="B62">
-        <v>9.955908374219135E-06</v>
+        <v>1.122523425934044E-05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pasteur</t>
+          <t>John Stuart Mill</t>
         </is>
       </c>
       <c r="B63">
-        <v>9.792352983826878E-06</v>
+        <v>1.10737985900165E-05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Oliver Wendell Holmes</t>
+          <t>Richard Cobden</t>
         </is>
       </c>
       <c r="B64">
-        <v>9.748321912398771E-06</v>
+        <v>1.107048578600068E-05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cicero</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B65">
-        <v>9.619325039553077E-06</v>
+        <v>1.096860089269015E-05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Leo Strauss</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B66">
-        <v>9.566733297070482E-06</v>
+        <v>1.084368447311948E-05</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Renan</t>
+          <t>Herodotus</t>
         </is>
       </c>
       <c r="B67">
-        <v>9.524942817160056E-06</v>
+        <v>1.074303056564703E-05</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="B68">
-        <v>9.369372605715892E-06</v>
+        <v>1.061250359309691E-05</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>John Woolman</t>
         </is>
       </c>
       <c r="B69">
-        <v>9.133227595910219E-06</v>
+        <v>1.058437629242224E-05</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>John Stuart Mill</t>
+          <t>Leibniz</t>
         </is>
       </c>
       <c r="B70">
-        <v>9.023679620563451E-06</v>
+        <v>1.045999247760161E-05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Robert Nozick</t>
+          <t>Thomas More</t>
         </is>
       </c>
       <c r="B71">
-        <v>8.794581393367949E-06</v>
+        <v>1.034769760329464E-05</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mazzini</t>
+          <t>William Graham Sumner</t>
         </is>
       </c>
       <c r="B72">
-        <v>8.76825472626054E-06</v>
+        <v>1.026241853329558E-05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Faraday</t>
+          <t>Pasteur</t>
         </is>
       </c>
       <c r="B73">
-        <v>8.602331692876998E-06</v>
+        <v>1.001635841339599E-05</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Montaigne</t>
+          <t>Cicero</t>
         </is>
       </c>
       <c r="B74">
-        <v>8.414760494317698E-06</v>
+        <v>1.00022498319259E-05</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Henry George</t>
+          <t>Faraday</t>
         </is>
       </c>
       <c r="B75">
-        <v>8.398286003392982E-06</v>
+        <v>9.910846158572475E-06</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Nassau Senior</t>
+          <t>Henry George</t>
         </is>
       </c>
       <c r="B76">
-        <v>8.38887149521329E-06</v>
+        <v>9.853059874280445E-06</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sismondi</t>
+          <t>Edward Bellamy</t>
         </is>
       </c>
       <c r="B77">
-        <v>8.354333404780524E-06</v>
+        <v>9.609671328295433E-06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Virgil</t>
+          <t>Isaiah Berlin</t>
         </is>
       </c>
       <c r="B78">
-        <v>7.965356245991246E-06</v>
+        <v>9.414118196785538E-06</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Kropotkin</t>
+          <t>Montaigne</t>
         </is>
       </c>
       <c r="B79">
-        <v>7.934249289204929E-06</v>
+        <v>9.392545862568922E-06</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tacitus</t>
+          <t>Raymond Aron</t>
         </is>
       </c>
       <c r="B80">
-        <v>7.657583142617749E-06</v>
+        <v>9.285191206247108E-06</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Goethe</t>
+          <t>Marlowe</t>
         </is>
       </c>
       <c r="B81">
-        <v>7.532811875628482E-06</v>
+        <v>9.174180578205455E-06</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Aristophanes</t>
+          <t>Edmund Burke</t>
         </is>
       </c>
       <c r="B82">
-        <v>7.44611911924923E-06</v>
+        <v>8.90705152556964E-06</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Rilke</t>
+          <t>Herder</t>
         </is>
       </c>
       <c r="B83">
-        <v>7.37027866448996E-06</v>
+        <v>8.778515647802025E-06</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Marlowe</t>
+          <t>Tacitus</t>
         </is>
       </c>
       <c r="B84">
-        <v>7.128378571370687E-06</v>
+        <v>8.727192472662936E-06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cervantes</t>
+          <t>Aristophanes</t>
         </is>
       </c>
       <c r="B85">
-        <v>7.091333103906583E-06</v>
+        <v>8.717932495142614E-06</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Proudhon</t>
+          <t>Virgil</t>
         </is>
       </c>
       <c r="B86">
-        <v>7.013828536310051E-06</v>
+        <v>8.678217867344398E-06</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Euripides</t>
+          <t>Cervantes</t>
         </is>
       </c>
       <c r="B87">
-        <v>6.98858484170702E-06</v>
+        <v>8.644375712506527E-06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Homer</t>
+          <t>Euripides</t>
         </is>
       </c>
       <c r="B88">
-        <v>6.927538224732879E-06</v>
+        <v>8.641997993083255E-06</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Herder</t>
+          <t>John Milton</t>
         </is>
       </c>
       <c r="B89">
-        <v>6.804969882630668E-06</v>
+        <v>8.583121481907283E-06</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Walt Whitman</t>
+          <t>Alexander Pope</t>
         </is>
       </c>
       <c r="B90">
-        <v>6.790960591718806E-06</v>
+        <v>8.557989036933057E-06</v>
       </c>
     </row>
     <row r="91">
@@ -2444,137 +2444,137 @@
         </is>
       </c>
       <c r="B91">
-        <v>6.78762473329352E-06</v>
+        <v>8.541444957735474E-06</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Edmund Burke</t>
+          <t>Walt Whitman</t>
         </is>
       </c>
       <c r="B92">
-        <v>6.669817948309744E-06</v>
+        <v>8.440905444796794E-06</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Froissart</t>
+          <t>Renan</t>
         </is>
       </c>
       <c r="B93">
-        <v>6.495770588436591E-06</v>
+        <v>8.374692913184592E-06</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Plato</t>
+          <t>David Ricardo</t>
         </is>
       </c>
       <c r="B94">
-        <v>6.36279593584575E-06</v>
+        <v>8.343587118605968E-06</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Durkheim</t>
+          <t>Mazzini</t>
         </is>
       </c>
       <c r="B95">
-        <v>6.354739667566448E-06</v>
+        <v>8.226076692215382E-06</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>John Milton</t>
+          <t>Goethe</t>
         </is>
       </c>
       <c r="B96">
-        <v>6.324066814101529E-06</v>
+        <v>8.110706328046421E-06</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Carl Friedrich</t>
+          <t>Thoreau</t>
         </is>
       </c>
       <c r="B97">
-        <v>6.26058054851418E-06</v>
+        <v>7.859389836280211E-06</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>John Ruskin</t>
         </is>
       </c>
       <c r="B98">
-        <v>6.250939813127616E-06</v>
+        <v>7.827261260308046E-06</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>John Woolman</t>
+          <t>Thomas Carlyle</t>
         </is>
       </c>
       <c r="B99">
-        <v>6.077285677928162E-06</v>
+        <v>7.803498221144143E-06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Richard Cobden</t>
+          <t>Sismondi</t>
         </is>
       </c>
       <c r="B100">
-        <v>6.060253851037473E-06</v>
+        <v>7.722109334786404E-06</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Alexander Pope</t>
+          <t>William Godwin</t>
         </is>
       </c>
       <c r="B101">
-        <v>5.9895021128527E-06</v>
+        <v>7.700485777957784E-06</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>William Graham Sumner</t>
+          <t>Durkheim</t>
         </is>
       </c>
       <c r="B102">
-        <v>5.785280355646223E-06</v>
+        <v>7.522486075127428E-06</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Thoreau</t>
+          <t>Rilke</t>
         </is>
       </c>
       <c r="B103">
-        <v>5.765097541418962E-06</v>
+        <v>7.455805439925454E-06</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Edward Bellamy</t>
+          <t>Jonathan Swift</t>
         </is>
       </c>
       <c r="B104">
-        <v>5.634739192260645E-06</v>
+        <v>7.364577759186619E-06</v>
       </c>
     </row>
     <row r="105">
@@ -2584,117 +2584,117 @@
         </is>
       </c>
       <c r="B105">
-        <v>5.59867151432537E-06</v>
+        <v>7.306848116406509E-06</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bakunin</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="B106">
-        <v>5.519548747304323E-06</v>
+        <v>7.229251777298651E-06</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>John Ruskin</t>
+          <t>Herbert Spencer</t>
         </is>
       </c>
       <c r="B107">
-        <v>5.288009546150756E-06</v>
+        <v>7.215554432559912E-06</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Herbert Spencer</t>
+          <t>Kropotkin</t>
         </is>
       </c>
       <c r="B108">
-        <v>5.228963971126837E-06</v>
+        <v>7.146616744870376E-06</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Isaiah Berlin</t>
+          <t>Lord Acton</t>
         </is>
       </c>
       <c r="B109">
-        <v>5.189568148386736E-06</v>
+        <v>7.090543081810606E-06</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Thomas Carlyle</t>
+          <t>Frederick Douglass</t>
         </is>
       </c>
       <c r="B110">
-        <v>5.166502621254449E-06</v>
+        <v>7.064296294052836E-06</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Hippocrates</t>
+          <t>Proudhon</t>
         </is>
       </c>
       <c r="B111">
-        <v>5.07531029999375E-06</v>
+        <v>7.051391529982857E-06</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Victor Hugo</t>
+          <t>Homer</t>
         </is>
       </c>
       <c r="B112">
-        <v>4.931130602451736E-06</v>
+        <v>7.003793782270449E-06</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>David Ricardo</t>
+          <t>Hippocrates</t>
         </is>
       </c>
       <c r="B113">
-        <v>4.831470736314893E-06</v>
+        <v>6.696131136468063E-06</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Jonathan Swift</t>
+          <t>Edmund Spenser</t>
         </is>
       </c>
       <c r="B114">
-        <v>4.744673677332425E-06</v>
+        <v>6.688326728181878E-06</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Aristotle</t>
+          <t>Froissart</t>
         </is>
       </c>
       <c r="B115">
-        <v>4.572855039644322E-06</v>
+        <v>6.475027813354587E-06</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>William Godwin</t>
+          <t>Max Weber</t>
         </is>
       </c>
       <c r="B116">
-        <v>4.537368970527289E-06</v>
+        <v>6.462602432273222E-06</v>
       </c>
     </row>
     <row r="117">
@@ -2704,17 +2704,17 @@
         </is>
       </c>
       <c r="B117">
-        <v>4.355261319541182E-06</v>
+        <v>6.276674231471915E-06</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Plato</t>
         </is>
       </c>
       <c r="B118">
-        <v>4.352735503938273E-06</v>
+        <v>6.262726787052719E-06</v>
       </c>
     </row>
     <row r="119">
@@ -2724,277 +2724,277 @@
         </is>
       </c>
       <c r="B119">
-        <v>4.337807407328505E-06</v>
+        <v>6.218804587228616E-06</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Frederick Douglass</t>
+          <t>Francis Bacon</t>
         </is>
       </c>
       <c r="B120">
-        <v>4.331508663267251E-06</v>
+        <v>6.003665919558201E-06</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Max Weber</t>
+          <t>Bakunin</t>
         </is>
       </c>
       <c r="B121">
-        <v>4.310531289319279E-06</v>
+        <v>5.976755383806543E-06</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Francis Bacon</t>
+          <t>Robert Owen</t>
         </is>
       </c>
       <c r="B122">
-        <v>4.274713017713401E-06</v>
+        <v>5.882304772883568E-06</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dostoyevsky</t>
+          <t>Victor Hugo</t>
         </is>
       </c>
       <c r="B123">
-        <v>3.949223709438939E-06</v>
+        <v>5.87808496439394E-06</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Edmund Spenser</t>
+          <t>Samuel Johnson</t>
         </is>
       </c>
       <c r="B124">
-        <v>3.765596677567363E-06</v>
+        <v>5.620354622526477E-06</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Schleiermacher</t>
+          <t>Thomas Mann</t>
         </is>
       </c>
       <c r="B125">
-        <v>3.765076727667441E-06</v>
+        <v>5.446719483462454E-06</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Voltaire</t>
+          <t>Charles Darwin</t>
         </is>
       </c>
       <c r="B126">
-        <v>3.625382158222615E-06</v>
+        <v>4.807860342546401E-06</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Robert Owen</t>
+          <t>Lord Byron</t>
         </is>
       </c>
       <c r="B127">
-        <v>3.576025380787425E-06</v>
+        <v>4.763575139972382E-06</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Thomas Mann</t>
+          <t>Malory</t>
         </is>
       </c>
       <c r="B128">
-        <v>3.568441095696959E-06</v>
+        <v>4.730498576921394E-06</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Cellini</t>
+          <t>Voltaire</t>
         </is>
       </c>
       <c r="B129">
-        <v>3.274097752009784E-06</v>
+        <v>4.708227560355985E-06</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Samuel Johnson</t>
+          <t>Aesop</t>
         </is>
       </c>
       <c r="B130">
-        <v>3.232550803825665E-06</v>
+        <v>4.571016640270338E-06</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Charles Darwin</t>
+          <t>Aristotle</t>
         </is>
       </c>
       <c r="B131">
-        <v>3.182259510476311E-06</v>
+        <v>4.470794944900397E-06</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Lord Byron</t>
+          <t>Simmel</t>
         </is>
       </c>
       <c r="B132">
-        <v>2.741012613314889E-06</v>
+        <v>4.416544690662701E-06</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Aesop</t>
+          <t>Ralph Waldo Emerson</t>
         </is>
       </c>
       <c r="B133">
-        <v>2.709029728613794E-06</v>
+        <v>4.356181487089925E-06</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Dilthey</t>
+          <t>Marcus Aurelius</t>
         </is>
       </c>
       <c r="B134">
-        <v>2.607358189352037E-06</v>
+        <v>4.235135266496981E-06</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Ranke</t>
+          <t>Dostoyevsky</t>
         </is>
       </c>
       <c r="B135">
-        <v>2.605399395678381E-06</v>
+        <v>4.184760231515755E-06</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Molière</t>
+          <t>Cellini</t>
         </is>
       </c>
       <c r="B136">
-        <v>2.58174142700187E-06</v>
+        <v>4.151243509120516E-06</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Marcus Aurelius</t>
+          <t>Ranke</t>
         </is>
       </c>
       <c r="B137">
-        <v>2.517646026316633E-06</v>
+        <v>4.040797407706364E-06</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ralph Waldo Emerson</t>
+          <t>John Knox</t>
         </is>
       </c>
       <c r="B138">
-        <v>2.408721977701095E-06</v>
+        <v>4.025405367860133E-06</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Malory</t>
+          <t>Wundt</t>
         </is>
       </c>
       <c r="B139">
-        <v>2.34519531636839E-06</v>
+        <v>3.921002708320961E-06</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Simmel</t>
+          <t>Molière</t>
         </is>
       </c>
       <c r="B140">
-        <v>2.189477059708186E-06</v>
+        <v>3.822035223800303E-06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Hamann</t>
+          <t>Robert Browning</t>
         </is>
       </c>
       <c r="B141">
-        <v>2.154723778704708E-06</v>
+        <v>3.785201799900853E-06</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Wundt</t>
+          <t>Robert Burns</t>
         </is>
       </c>
       <c r="B142">
-        <v>2.11156064801189E-06</v>
+        <v>3.747787965402377E-06</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>John Calvin</t>
+          <t>Izaak Walton</t>
         </is>
       </c>
       <c r="B143">
-        <v>2.004583139588825E-06</v>
+        <v>3.720378155607952E-06</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>John Knox</t>
+          <t>Walter Raleigh</t>
         </is>
       </c>
       <c r="B144">
-        <v>1.998496183358313E-06</v>
+        <v>3.609746745696988E-06</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Izaak Walton</t>
+          <t>Schleiermacher</t>
         </is>
       </c>
       <c r="B145">
-        <v>1.919897398826592E-06</v>
+        <v>3.494103666042299E-06</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Robert Burns</t>
+          <t>Talcott Parsons</t>
         </is>
       </c>
       <c r="B146">
-        <v>1.915094498474714E-06</v>
+        <v>3.4723442308081E-06</v>
       </c>
     </row>
     <row r="147">
@@ -3004,507 +3004,507 @@
         </is>
       </c>
       <c r="B147">
-        <v>1.890283309775712E-06</v>
+        <v>3.305920768223282E-06</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Walter Raleigh</t>
+          <t>Scheler</t>
         </is>
       </c>
       <c r="B148">
-        <v>1.809402276636385E-06</v>
+        <v>3.145500282397035E-06</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Robert Browning</t>
+          <t>John Calvin</t>
         </is>
       </c>
       <c r="B149">
-        <v>1.796957237857337E-06</v>
+        <v>3.140772990740541E-06</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Auguste Comte</t>
+          <t>William Wordsworth</t>
         </is>
       </c>
       <c r="B150">
-        <v>1.770882925349659E-06</v>
+        <v>3.089898846684451E-06</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Scheler</t>
+          <t>Thomas Browne</t>
         </is>
       </c>
       <c r="B151">
-        <v>1.667489694486173E-06</v>
+        <v>2.904820969147434E-06</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>William Harvey</t>
+          <t>Hans Christian Andersen</t>
         </is>
       </c>
       <c r="B152">
-        <v>1.625120978567457E-06</v>
+        <v>2.850555237254809E-06</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Hans Christian Andersen</t>
+          <t>Herbart</t>
         </is>
       </c>
       <c r="B153">
-        <v>1.485230474484102E-06</v>
+        <v>2.779036417576013E-06</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Dante Alighieri</t>
+          <t>Hamann</t>
         </is>
       </c>
       <c r="B154">
-        <v>1.479707734979292E-06</v>
+        <v>2.743598613759221E-06</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Herbart</t>
+          <t>Auguste Comte</t>
         </is>
       </c>
       <c r="B155">
-        <v>1.454826141718271E-06</v>
+        <v>2.74358934510328E-06</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Talcott Parsons</t>
+          <t>Frege</t>
         </is>
       </c>
       <c r="B156">
-        <v>1.447881799765796E-06</v>
+        <v>2.709303318091319E-06</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Kempis</t>
+          <t>William Harvey</t>
         </is>
       </c>
       <c r="B157">
-        <v>1.411331361090731E-06</v>
+        <v>2.705543612414525E-06</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>William Wordsworth</t>
+          <t>Dilthey</t>
         </is>
       </c>
       <c r="B158">
-        <v>1.401690368204195E-06</v>
+        <v>2.699474809985092E-06</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Thomas Browne</t>
+          <t>Henry Fielding</t>
         </is>
       </c>
       <c r="B159">
-        <v>1.271512941329109E-06</v>
+        <v>2.607803451377968E-06</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Hölderlin</t>
+          <t>John Bunyan</t>
         </is>
       </c>
       <c r="B160">
-        <v>1.243275759313155E-06</v>
+        <v>2.576305856948499E-06</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>John Bunyan</t>
+          <t>Oliver Goldsmith</t>
         </is>
       </c>
       <c r="B161">
-        <v>1.14130882242043E-06</v>
+        <v>2.531337392655552E-06</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Hippolyte Taine</t>
+          <t>Kempis</t>
         </is>
       </c>
       <c r="B162">
-        <v>1.130815940641157E-06</v>
+        <v>2.5256795016844E-06</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Henry Fielding</t>
+          <t>Dante Alighieri</t>
         </is>
       </c>
       <c r="B163">
-        <v>1.128299559216669E-06</v>
+        <v>2.404196035872552E-06</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Karl Jaspers</t>
+          <t>William Harrison</t>
         </is>
       </c>
       <c r="B164">
-        <v>1.096138379120399E-06</v>
+        <v>2.310707025397623E-06</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Alessandro Manzoni</t>
+          <t>Percy Bysshe Shelley</t>
         </is>
       </c>
       <c r="B165">
-        <v>1.081862127791888E-06</v>
+        <v>2.294739221859019E-06</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ebbinghaus</t>
+          <t>Hölderlin</t>
         </is>
       </c>
       <c r="B166">
-        <v>1.076190599296933E-06</v>
+        <v>2.155716705519169E-06</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Jean Racine</t>
+          <t>Pliny the Younger</t>
         </is>
       </c>
       <c r="B167">
-        <v>1.072746129477842E-06</v>
+        <v>2.021216201824462E-06</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Oliver Goldsmith</t>
+          <t>William Caxton</t>
         </is>
       </c>
       <c r="B168">
-        <v>1.072013715575292E-06</v>
+        <v>2.011864243062071E-06</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sainte Beuve</t>
+          <t>Robert Merton</t>
         </is>
       </c>
       <c r="B169">
-        <v>1.067253385870288E-06</v>
+        <v>1.959480023774383E-06</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Pierre Corneille</t>
+          <t>Edward Jenner</t>
         </is>
       </c>
       <c r="B170">
-        <v>1.056468861921444E-06</v>
+        <v>1.893350587538667E-06</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ernst Cassirer</t>
+          <t>Simon Newcomb</t>
         </is>
       </c>
       <c r="B171">
-        <v>1.049136696353885E-06</v>
+        <v>1.879205715858623E-06</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Windelband</t>
+          <t>Joseph Lister</t>
         </is>
       </c>
       <c r="B172">
-        <v>1.023573726354782E-06</v>
+        <v>1.863975029401186E-06</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Pliny the Younger</t>
+          <t>Pierre Corneille</t>
         </is>
       </c>
       <c r="B173">
-        <v>1.002726307123421E-06</v>
+        <v>1.841081550654891E-06</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ambroise Paré</t>
+          <t>Archibald Geikie</t>
         </is>
       </c>
       <c r="B174">
-        <v>9.94765941191566E-07</v>
+        <v>1.811951583427197E-06</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Percy Bysshe Shelley</t>
+          <t>Jean Racine</t>
         </is>
       </c>
       <c r="B175">
-        <v>9.663333207726255E-07</v>
+        <v>1.811907962110303E-06</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>William Harrison</t>
+          <t>Hippolyte Taine</t>
         </is>
       </c>
       <c r="B176">
-        <v>9.082480529972156E-07</v>
+        <v>1.808527456104704E-06</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Hermann Cohen</t>
+          <t>Karl Jaspers</t>
         </is>
       </c>
       <c r="B177">
-        <v>8.922175312345153E-07</v>
+        <v>1.796992223271787E-06</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Carl Stumpf</t>
+          <t>Otto Pfleiderer</t>
         </is>
       </c>
       <c r="B178">
-        <v>8.854417582192851E-07</v>
+        <v>1.785821110586856E-06</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Bernard Bolzano</t>
+          <t>Sainte Beuve</t>
         </is>
       </c>
       <c r="B179">
-        <v>8.803551213953385E-07</v>
+        <v>1.776975793212368E-06</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Friedrich Heinrich Jacobi</t>
+          <t>Ernst Cassirer</t>
         </is>
       </c>
       <c r="B180">
-        <v>8.739051346783866E-07</v>
+        <v>1.769927275744798E-06</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Heinrich Rickert</t>
+          <t>Alessandro Manzoni</t>
         </is>
       </c>
       <c r="B181">
-        <v>8.712022975533111E-07</v>
+        <v>1.769098832932304E-06</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Grimmelshausen</t>
+          <t>Philip Nichols</t>
         </is>
       </c>
       <c r="B182">
-        <v>8.68280930418352E-07</v>
+        <v>1.74515464290507E-06</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Franz Brentano</t>
+          <t>Ambroise Paré</t>
         </is>
       </c>
       <c r="B183">
-        <v>8.616141351808751E-07</v>
+        <v>1.735901301801387E-06</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Thünen</t>
+          <t>William Roper</t>
         </is>
       </c>
       <c r="B184">
-        <v>8.551843088302906E-07</v>
+        <v>1.717359864656436E-06</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Norbert Elias</t>
+          <t>Bigges</t>
         </is>
       </c>
       <c r="B185">
-        <v>8.381673680639689E-07</v>
+        <v>1.702072948187563E-06</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Friedrich Schiller</t>
+          <t>Pedro Calderón de la Barca</t>
         </is>
       </c>
       <c r="B186">
-        <v>8.334533855656261E-07</v>
+        <v>1.681356848399934E-06</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Eduard von Hartmann</t>
+          <t>Francis Pretty</t>
         </is>
       </c>
       <c r="B187">
-        <v>8.315112786087338E-07</v>
+        <v>1.676789095683103E-06</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Theodor Fontane</t>
+          <t>Edward Haies</t>
         </is>
       </c>
       <c r="B188">
-        <v>8.274931805254717E-07</v>
+        <v>1.673814919407043E-06</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Külpe</t>
+          <t>Grimmelshausen</t>
         </is>
       </c>
       <c r="B189">
-        <v>8.271347124733718E-07</v>
+        <v>1.530175565356268E-06</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Eduard Zeller</t>
+          <t>Windelband</t>
         </is>
       </c>
       <c r="B190">
-        <v>8.269500675106746E-07</v>
+        <v>1.516960455418976E-06</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Hermann Lotze</t>
+          <t>Thünen</t>
         </is>
       </c>
       <c r="B191">
-        <v>8.249053207142056E-07</v>
+        <v>1.308489924443473E-06</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Gustav Freytag</t>
+          <t>Eduard von Hartmann</t>
         </is>
       </c>
       <c r="B192">
-        <v>8.146896382836196E-07</v>
+        <v>1.049964029934078E-06</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Edward Jenner</t>
+          <t>Ebbinghaus</t>
         </is>
       </c>
       <c r="B193">
-        <v>8.135892618347214E-07</v>
+        <v>1.031880535331186E-06</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Ludwig Büchner</t>
+          <t>Hermann Cohen</t>
         </is>
       </c>
       <c r="B194">
-        <v>8.072072494944462E-07</v>
+        <v>1.006179851787722E-06</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Gotthold Ephraim Lessing</t>
+          <t>Eduard Zeller</t>
         </is>
       </c>
       <c r="B195">
-        <v>7.984079971473498E-07</v>
+        <v>9.838818814182808E-07</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Friedrich Carl von Savigny</t>
+          <t>Friedrich Heinrich Jacobi</t>
         </is>
       </c>
       <c r="B196">
-        <v>7.975102677767314E-07</v>
+        <v>9.743095310313314E-07</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Joseph Lister</t>
+          <t>Gustav Freytag</t>
         </is>
       </c>
       <c r="B197">
-        <v>7.933979408752159E-07</v>
+        <v>9.736969558513394E-07</v>
       </c>
     </row>
     <row r="198">
@@ -3514,157 +3514,157 @@
         </is>
       </c>
       <c r="B198">
-        <v>7.890310628641462E-07</v>
+        <v>9.720168194792511E-07</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>E T A Hoffmann</t>
+          <t>Gotthold Ephraim Lessing</t>
         </is>
       </c>
       <c r="B199">
-        <v>7.858494924721274E-07</v>
+        <v>9.680063441446461E-07</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Robert Merton</t>
+          <t>Hermann Lotze</t>
         </is>
       </c>
       <c r="B200">
-        <v>7.810273530668108E-07</v>
+        <v>9.557278635136708E-07</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Pedro Calderón de la Barca</t>
+          <t>Bernard Bolzano</t>
         </is>
       </c>
       <c r="B201">
-        <v>7.767959730478807E-07</v>
+        <v>9.549822613041442E-07</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Simon Newcomb</t>
+          <t>Friedrich Carl von Savigny</t>
         </is>
       </c>
       <c r="B202">
-        <v>7.669106666789703E-07</v>
+        <v>9.535183309464001E-07</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>William Caxton</t>
+          <t>Heinrich Rickert</t>
         </is>
       </c>
       <c r="B203">
-        <v>7.460969245702876E-07</v>
+        <v>9.462601347432618E-07</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Archibald Geikie</t>
+          <t>E T A Hoffmann</t>
         </is>
       </c>
       <c r="B204">
-        <v>7.30725340466985E-07</v>
+        <v>9.401208377776082E-07</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Otto Pfleiderer</t>
+          <t>Ludwig Büchner</t>
         </is>
       </c>
       <c r="B205">
-        <v>7.254442536812366E-07</v>
+        <v>9.262489521704766E-07</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Frege</t>
+          <t>Carl Stumpf</t>
         </is>
       </c>
       <c r="B206">
-        <v>6.983898432859817E-07</v>
+        <v>9.168986475971577E-07</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>William Roper</t>
+          <t>Friedrich Schiller</t>
         </is>
       </c>
       <c r="B207">
-        <v>6.914704619555264E-07</v>
+        <v>9.156739394598017E-07</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Philip Nichols</t>
+          <t>Franz Brentano</t>
         </is>
       </c>
       <c r="B208">
-        <v>6.709236222318161E-07</v>
+        <v>8.911134862871982E-07</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Bigges</t>
+          <t>Külpe</t>
         </is>
       </c>
       <c r="B209">
-        <v>6.354405675508554E-07</v>
+        <v>8.405347395207391E-07</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Edward Haies</t>
+          <t>Theodor Fontane</t>
         </is>
       </c>
       <c r="B210">
-        <v>6.239097099275735E-07</v>
+        <v>7.784111522720706E-07</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Francis Pretty</t>
+          <t>Newton</t>
         </is>
       </c>
       <c r="B211">
-        <v>6.233320753835831E-07</v>
+        <v>2.793348714965969E-07</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Newton</t>
+          <t>John Rawls</t>
         </is>
       </c>
       <c r="B212">
-        <v>2.93986990936149E-07</v>
+        <v>1.409876080974224E-08</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>John Rawls</t>
+          <t>Norbert Elias</t>
         </is>
       </c>
       <c r="B213">
-        <v>6.101726703870267E-09</v>
+        <v>4.813203674745916E-09</v>
       </c>
     </row>
   </sheetData>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.00225890031804267</v>
+        <v>0.00150798542894669</v>
       </c>
     </row>
     <row r="3">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.0007710589194695836</v>
+        <v>0.0001898064413677563</v>
       </c>
     </row>
     <row r="22">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.0002851216159125356</v>
+        <v>0.0005121571292196323</v>
       </c>
     </row>
     <row r="41">
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.00350790094842442</v>
+        <v>0.00100323198446292</v>
       </c>
     </row>
     <row r="60">
@@ -4456,7 +4456,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.002073255062214717</v>
+        <v>0.001022573297691636</v>
       </c>
     </row>
     <row r="79">
@@ -4646,7 +4646,7 @@
         </is>
       </c>
       <c r="B97">
-        <v>0.002506319382828331</v>
+        <v>0.0004187117352252478</v>
       </c>
     </row>
     <row r="98">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="B116">
-        <v>0.001604222676178732</v>
+        <v>0.0005806178243771761</v>
       </c>
     </row>
     <row r="117">
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="B135">
-        <v>0.001301062199853535</v>
+        <v>0.0001849894455971948</v>
       </c>
     </row>
     <row r="136">
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="B154">
-        <v>0.0004818212203600514</v>
+        <v>0.0009305192335835573</v>
       </c>
     </row>
     <row r="155">
@@ -5406,7 +5406,7 @@
         </is>
       </c>
       <c r="B173">
-        <v>4.398554670033234E-05</v>
+        <v>7.615494591254494E-05</v>
       </c>
     </row>
     <row r="174">
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="B192">
-        <v>0.007435078791505647</v>
+        <v>0.007169146320861126</v>
       </c>
     </row>
     <row r="193">
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="B211">
-        <v>0.1384295005020705</v>
+        <v>0.1365170485279525</v>
       </c>
     </row>
     <row r="212">
@@ -5976,7 +5976,7 @@
         </is>
       </c>
       <c r="B230">
-        <v>0.1305064094996717</v>
+        <v>0.1344567562235189</v>
       </c>
     </row>
     <row r="231">
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="B249">
-        <v>0.1291887934390043</v>
+        <v>0.1324498823887196</v>
       </c>
     </row>
     <row r="250">
@@ -6356,7 +6356,7 @@
         </is>
       </c>
       <c r="B268">
-        <v>0.1190849906982511</v>
+        <v>0.1193038260143512</v>
       </c>
     </row>
     <row r="269">
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="B287">
-        <v>0.1410824059547091</v>
+        <v>0.1406220758397632</v>
       </c>
     </row>
     <row r="288">
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="B306">
-        <v>0.1599756916195188</v>
+        <v>0.1659469039619304</v>
       </c>
     </row>
     <row r="307">
@@ -6926,7 +6926,7 @@
         </is>
       </c>
       <c r="B325">
-        <v>0.1594634816052838</v>
+        <v>0.1571076132565187</v>
       </c>
     </row>
   </sheetData>
@@ -6966,7 +6966,7 @@
         <v>0.9828230022404779</v>
       </c>
       <c r="C2">
-        <v>0.9783539701426395</v>
+        <v>0.9783608985303387</v>
       </c>
     </row>
     <row r="3">
@@ -6979,7 +6979,7 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.03763773076601178</v>
+        <v>0.03745357248085106</v>
       </c>
     </row>
     <row r="4">
@@ -6992,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.9613208552728527</v>
+        <v>0.9617127647613481</v>
       </c>
     </row>
     <row r="5">
@@ -7005,7 +7005,7 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.0003550507733154804</v>
+        <v>0.0002862380192466214</v>
       </c>
     </row>
     <row r="6">
@@ -7018,7 +7018,7 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.0001022380091687906</v>
+        <v>0.0001165720339329036</v>
       </c>
     </row>
     <row r="7">
@@ -7031,7 +7031,7 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.0001334481723457009</v>
+        <v>0.000128417654474091</v>
       </c>
     </row>
     <row r="8">
@@ -7044,7 +7044,7 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.0004620567914850122</v>
+        <v>0.0003443231631429474</v>
       </c>
     </row>
     <row r="9">
@@ -7057,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>7.868129076954464E-06</v>
+        <v>1.032573256090646E-05</v>
       </c>
     </row>
     <row r="10">
@@ -7070,7 +7070,7 @@
         <v>0.9381107491856677</v>
       </c>
       <c r="C10">
-        <v>0.936511100719528</v>
+        <v>0.9371687514441869</v>
       </c>
     </row>
     <row r="11">
@@ -7083,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="C11">
-        <v>0.9463892695061986</v>
+        <v>0.945317137886325</v>
       </c>
     </row>
     <row r="12">
@@ -7096,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>0.9847337089856718</v>
+        <v>0.9833865653939138</v>
       </c>
     </row>
     <row r="13">
@@ -7106,10 +7106,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.003214611872146118</v>
+        <v>0.003220742523444055</v>
       </c>
       <c r="C13">
-        <v>0.002692049434698579</v>
+        <v>0.002678957980544751</v>
       </c>
     </row>
     <row r="14">
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.002952054794520548</v>
+        <v>0.002958034966677906</v>
       </c>
       <c r="C14">
-        <v>0.001992244252999115</v>
+        <v>0.00201590608802024</v>
       </c>
     </row>
     <row r="15">
@@ -7132,10 +7132,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.0007710045662100456</v>
+        <v>0.0007722042687907591</v>
       </c>
       <c r="C15">
-        <v>0.001503273306902666</v>
+        <v>0.001499584933469845</v>
       </c>
     </row>
     <row r="16">
@@ -7145,10 +7145,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.0009178082191780821</v>
+        <v>0.0009208178774211453</v>
       </c>
       <c r="C16">
-        <v>0.001317613877632355</v>
+        <v>0.001309366393198863</v>
       </c>
     </row>
     <row r="17">
@@ -7158,10 +7158,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.0008538812785388127</v>
+        <v>0.000855931413511149</v>
       </c>
       <c r="C17">
-        <v>0.001217086944519727</v>
+        <v>0.001203947052609518</v>
       </c>
     </row>
     <row r="18">
@@ -7171,10 +7171,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.0007315068493150684</v>
+        <v>0.0007318812200025874</v>
       </c>
       <c r="C18">
-        <v>0.00112675596601584</v>
+        <v>0.001128566444633609</v>
       </c>
     </row>
     <row r="19">
@@ -7184,10 +7184,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>0.0007602739726027397</v>
+        <v>0.0007618847045602425</v>
       </c>
       <c r="C19">
-        <v>0.0006380796549306509</v>
+        <v>0.0006476152039236139</v>
       </c>
     </row>
   </sheetData>
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>14.45843964170053</v>
+        <v>14.48697428394893</v>
       </c>
     </row>
     <row r="3">
@@ -7271,7 +7271,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>14.45843964170053</v>
+        <v>14.48697428394893</v>
       </c>
     </row>
     <row r="3">
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>9.311555617382878</v>
+        <v>9.310249994514981</v>
       </c>
     </row>
     <row r="4">
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>8.910162898169622</v>
+        <v>8.789176718337878</v>
       </c>
     </row>
     <row r="5">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>8.518953516167361</v>
+        <v>7.695509410561466</v>
       </c>
     </row>
     <row r="6">
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>6.800150809504602</v>
+        <v>6.815529759795489</v>
       </c>
     </row>
     <row r="7">
@@ -7321,7 +7321,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>6.040549573854437</v>
+        <v>6.045800723830406</v>
       </c>
     </row>
     <row r="8">
@@ -7331,7 +7331,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>5.88344235603585</v>
+        <v>5.850997551352893</v>
       </c>
     </row>
     <row r="9">
@@ -7341,207 +7341,207 @@
         </is>
       </c>
       <c r="B9">
-        <v>5.35004034049827</v>
+        <v>5.399136001165108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Oswald Spengler</t>
+          <t>Norbert Elias</t>
         </is>
       </c>
       <c r="B10">
-        <v>5.276546629498767</v>
+        <v>5.091665923377615</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norbert Elias</t>
+          <t>Oswald Spengler</t>
         </is>
       </c>
       <c r="B11">
-        <v>4.769700682130605</v>
+        <v>4.963654609049848</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Epictetus</t>
+          <t>Ferdinand Tönnies</t>
         </is>
       </c>
       <c r="B12">
-        <v>4.746739449498637</v>
+        <v>4.912939767633963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Aquinas</t>
+          <t>Theodor Fontane</t>
         </is>
       </c>
       <c r="B13">
-        <v>4.627446978795009</v>
+        <v>4.775288291625082</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hans Kelsen</t>
+          <t>Epictetus</t>
         </is>
       </c>
       <c r="B14">
-        <v>4.37171107572275</v>
+        <v>4.736444594813943</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Julius Evola</t>
+          <t>John Calvin</t>
         </is>
       </c>
       <c r="B15">
-        <v>3.997265232112186</v>
+        <v>4.691410171709716</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pliny the Younger</t>
+          <t>Aquinas</t>
         </is>
       </c>
       <c r="B16">
-        <v>3.883904598401175</v>
+        <v>4.641510774386794</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Theodor Fontane</t>
+          <t>William Harvey</t>
         </is>
       </c>
       <c r="B17">
-        <v>3.86536795814953</v>
+        <v>4.095817031291693</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>John Ruskin</t>
+          <t>Julius Evola</t>
         </is>
       </c>
       <c r="B18">
-        <v>3.858998816969589</v>
+        <v>3.90786747238199</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Oliver Goldsmith</t>
+          <t>Leibniz</t>
         </is>
       </c>
       <c r="B19">
-        <v>3.730622850727787</v>
+        <v>3.818449776090945</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>John Calvin</t>
+          <t>Arthur Moeller van den Bruck</t>
         </is>
       </c>
       <c r="B20">
-        <v>3.635862254095275</v>
+        <v>3.74368993583871</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Leibniz</t>
+          <t>James Madison</t>
         </is>
       </c>
       <c r="B21">
-        <v>3.597792436658046</v>
+        <v>3.722301065049635</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ferdinand Tönnies</t>
+          <t>Oliver Goldsmith</t>
         </is>
       </c>
       <c r="B22">
-        <v>3.579572555508145</v>
+        <v>3.66064247991857</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ralph Waldo Emerson</t>
+          <t>Frederick Douglass</t>
         </is>
       </c>
       <c r="B23">
-        <v>3.537560866006781</v>
+        <v>3.610995134060863</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ambroise Paré</t>
+          <t>Ralph Waldo Emerson</t>
         </is>
       </c>
       <c r="B24">
-        <v>3.461705273987822</v>
+        <v>3.526621247080377</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>William Harvey</t>
+          <t>Descartes</t>
         </is>
       </c>
       <c r="B25">
-        <v>3.344894493031163</v>
+        <v>3.523243272128199</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Frederick Douglass</t>
+          <t>Pliny the Younger</t>
         </is>
       </c>
       <c r="B26">
-        <v>3.313980887497486</v>
+        <v>3.516381138348736</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wollstonecraft</t>
+          <t>Oliver Wendell Holmes</t>
         </is>
       </c>
       <c r="B27">
-        <v>3.304883690088922</v>
+        <v>3.488165306733082</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hobbes</t>
+          <t>Ambroise Paré</t>
         </is>
       </c>
       <c r="B28">
-        <v>3.243436335584689</v>
+        <v>3.478908940559567</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Schäffle</t>
+          <t>Hans Kelsen</t>
         </is>
       </c>
       <c r="B29">
-        <v>3.232142706327895</v>
+        <v>3.420218276322792</v>
       </c>
     </row>
     <row r="30">
@@ -7551,27 +7551,27 @@
         </is>
       </c>
       <c r="B30">
-        <v>3.227463557030425</v>
+        <v>3.371771984184221</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Herodotus</t>
+          <t>John Ruskin</t>
         </is>
       </c>
       <c r="B31">
-        <v>3.212054007198904</v>
+        <v>3.307710841818293</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Spinoza</t>
+          <t>Schäffle</t>
         </is>
       </c>
       <c r="B32">
-        <v>3.109435647815987</v>
+        <v>3.29070321422155</v>
       </c>
     </row>
     <row r="33">
@@ -7581,57 +7581,57 @@
         </is>
       </c>
       <c r="B33">
-        <v>3.107508590834184</v>
+        <v>3.164333676726876</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oliver Wendell Holmes</t>
+          <t>Herodotus</t>
         </is>
       </c>
       <c r="B34">
-        <v>3.100435570150809</v>
+        <v>3.160149179243148</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Edward Bellamy</t>
+          <t>Hobbes</t>
         </is>
       </c>
       <c r="B35">
-        <v>3.076602676120474</v>
+        <v>3.111628475704786</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Descartes</t>
+          <t>Spinoza</t>
         </is>
       </c>
       <c r="B36">
-        <v>2.952564150237928</v>
+        <v>3.100477259041342</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hans Christian Andersen</t>
+          <t>Thomas More</t>
         </is>
       </c>
       <c r="B37">
-        <v>2.911879705150323</v>
+        <v>2.944011374263079</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>James Madison</t>
+          <t>Edward Bellamy</t>
         </is>
       </c>
       <c r="B38">
-        <v>2.900998604831149</v>
+        <v>2.92393398431802</v>
       </c>
     </row>
     <row r="39">
@@ -7641,47 +7641,47 @@
         </is>
       </c>
       <c r="B39">
-        <v>2.874391573026193</v>
+        <v>2.875470788600578</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Hermann Cohen</t>
+          <t>Helmholtz</t>
         </is>
       </c>
       <c r="B40">
-        <v>2.720315870836978</v>
+        <v>2.872479943938108</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>John Stuart Mill</t>
+          <t>Alexander Pope</t>
         </is>
       </c>
       <c r="B41">
-        <v>2.683540008904877</v>
+        <v>2.831704900649164</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Schleiermacher</t>
+          <t>Marcus Aurelius</t>
         </is>
       </c>
       <c r="B42">
-        <v>2.59924863428019</v>
+        <v>2.822542472664316</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Helmholtz</t>
+          <t>Hermann Cohen</t>
         </is>
       </c>
       <c r="B43">
-        <v>2.579868562466978</v>
+        <v>2.757804699817352</v>
       </c>
     </row>
     <row r="44">
@@ -7691,247 +7691,247 @@
         </is>
       </c>
       <c r="B44">
-        <v>2.543316441074916</v>
+        <v>2.670119163584452</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hölderlin</t>
+          <t>Schleiermacher</t>
         </is>
       </c>
       <c r="B45">
-        <v>2.518599932544549</v>
+        <v>2.610714550373816</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kelvin</t>
+          <t>Gaetano Mosca</t>
         </is>
       </c>
       <c r="B46">
-        <v>2.513879800167524</v>
+        <v>2.579689957935843</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Molière</t>
+          <t>Kempis</t>
         </is>
       </c>
       <c r="B47">
-        <v>2.500035474043251</v>
+        <v>2.554638854318859</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>William Roper</t>
+          <t>Tocqueville</t>
         </is>
       </c>
       <c r="B48">
-        <v>2.453309512445219</v>
+        <v>2.483488485577365</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>David Ricardo</t>
+          <t>William Roper</t>
         </is>
       </c>
       <c r="B49">
-        <v>2.397183519479709</v>
+        <v>2.48030664280604</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>John Bunyan</t>
+          <t>Izaak Walton</t>
         </is>
       </c>
       <c r="B50">
-        <v>2.369963256628656</v>
+        <v>2.450218053158968</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gaetano Mosca</t>
+          <t>Wollstonecraft</t>
         </is>
       </c>
       <c r="B51">
-        <v>2.369448502672439</v>
+        <v>2.432449709483722</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Gustav Freytag</t>
+          <t>William Graham Sumner</t>
         </is>
       </c>
       <c r="B52">
-        <v>2.321109361474781</v>
+        <v>2.392245644031415</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Victor Hugo</t>
+          <t>Benjamin Franklin</t>
         </is>
       </c>
       <c r="B53">
-        <v>2.302043323097432</v>
+        <v>2.377580220897511</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alexander Pope</t>
+          <t>Ferdinand Lassalle</t>
         </is>
       </c>
       <c r="B54">
-        <v>2.277496444223678</v>
+        <v>2.356335568478662</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Homer</t>
+          <t>David Ricardo</t>
         </is>
       </c>
       <c r="B55">
-        <v>2.268752568184499</v>
+        <v>2.344853809971976</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Faraday</t>
+          <t>Gustav Freytag</t>
         </is>
       </c>
       <c r="B56">
-        <v>2.267156826955119</v>
+        <v>2.330862626798984</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Benjamin Franklin</t>
+          <t>Hans Christian Andersen</t>
         </is>
       </c>
       <c r="B57">
-        <v>2.256010387629619</v>
+        <v>2.287255208433658</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Edgar Jung</t>
+          <t>Faraday</t>
         </is>
       </c>
       <c r="B58">
-        <v>2.24603285186156</v>
+        <v>2.278858942210992</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Augustine</t>
+          <t>Homer</t>
         </is>
       </c>
       <c r="B59">
-        <v>2.245144229157667</v>
+        <v>2.261866543606742</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>E T A Hoffmann</t>
+          <t>Edgar Jung</t>
         </is>
       </c>
       <c r="B60">
-        <v>2.210835672785483</v>
+        <v>2.246703535979851</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machiavelli</t>
+          <t>E T A Hoffmann</t>
         </is>
       </c>
       <c r="B61">
-        <v>2.194510369282808</v>
+        <v>2.236552033510651</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Izaak Walton</t>
+          <t>Thucydides</t>
         </is>
       </c>
       <c r="B62">
-        <v>2.15045253633587</v>
+        <v>2.185071972891957</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Kafka</t>
+          <t>Augustine</t>
         </is>
       </c>
       <c r="B63">
-        <v>2.132565051506983</v>
+        <v>2.172208934438139</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Pierre Corneille</t>
+          <t>Kafka</t>
         </is>
       </c>
       <c r="B64">
-        <v>2.12839536543473</v>
+        <v>2.145890248263637</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sainte Beuve</t>
+          <t>Machiavelli</t>
         </is>
       </c>
       <c r="B65">
-        <v>2.115310878219616</v>
+        <v>2.120622377384741</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Friedrich List</t>
+          <t>Külpe</t>
         </is>
       </c>
       <c r="B66">
-        <v>2.111721602704933</v>
+        <v>2.115401643572359</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kempis</t>
+          <t>Sainte Beuve</t>
         </is>
       </c>
       <c r="B67">
-        <v>2.109008087031987</v>
+        <v>2.113760461963327</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Külpe</t>
+          <t>Friedrich List</t>
         </is>
       </c>
       <c r="B68">
-        <v>2.104901482905361</v>
+        <v>2.100443233673433</v>
       </c>
     </row>
     <row r="69">
@@ -7941,127 +7941,127 @@
         </is>
       </c>
       <c r="B69">
-        <v>2.086315591837873</v>
+        <v>2.075017837305089</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Thomas More</t>
+          <t>Kelvin</t>
         </is>
       </c>
       <c r="B70">
-        <v>2.028771907309684</v>
+        <v>2.037336069865039</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Marlowe</t>
+          <t>John C Calhoun</t>
         </is>
       </c>
       <c r="B71">
-        <v>2.027020846524906</v>
+        <v>2.022598663216493</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ferdinand Lassalle</t>
+          <t>Eduard Bernstein</t>
         </is>
       </c>
       <c r="B72">
-        <v>2.000490807759302</v>
+        <v>1.966040080702247</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Eduard Bernstein</t>
+          <t>Franz Brentano</t>
         </is>
       </c>
       <c r="B73">
-        <v>1.989589814483148</v>
+        <v>1.885826361817297</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Wilhelm von Humboldt</t>
+          <t>Windelband</t>
         </is>
       </c>
       <c r="B74">
-        <v>1.912292755786223</v>
+        <v>1.884013184670368</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Franz Brentano</t>
+          <t>Aeschylus</t>
         </is>
       </c>
       <c r="B75">
-        <v>1.904250406501657</v>
+        <v>1.849789365136884</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>William Graham Sumner</t>
+          <t>Abraham Lincoln</t>
         </is>
       </c>
       <c r="B76">
-        <v>1.90244137105349</v>
+        <v>1.829453108510856</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Aeschylus</t>
+          <t>Pierre Corneille</t>
         </is>
       </c>
       <c r="B77">
-        <v>1.892378586509494</v>
+        <v>1.79618535479539</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Charles Fourier</t>
+          <t>Clausewitz</t>
         </is>
       </c>
       <c r="B78">
-        <v>1.884742731804598</v>
+        <v>1.793977979980034</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Eduard Zeller</t>
+          <t>Grimmelshausen</t>
         </is>
       </c>
       <c r="B79">
-        <v>1.880367296960094</v>
+        <v>1.788528320436893</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Henry George</t>
+          <t>Raymond Aron</t>
         </is>
       </c>
       <c r="B80">
-        <v>1.877649616431016</v>
+        <v>1.737675384784624</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Windelband</t>
+          <t>Virgil</t>
         </is>
       </c>
       <c r="B81">
-        <v>1.871718708171272</v>
+        <v>1.729486012734673</v>
       </c>
     </row>
     <row r="82">
@@ -8071,87 +8071,87 @@
         </is>
       </c>
       <c r="B82">
-        <v>1.818465694960427</v>
+        <v>1.706294091307536</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Clausewitz</t>
+          <t>Frege</t>
         </is>
       </c>
       <c r="B83">
-        <v>1.795246958487236</v>
+        <v>1.701157879655089</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Grimmelshausen</t>
+          <t>Thomas Mann</t>
         </is>
       </c>
       <c r="B84">
-        <v>1.787958308358375</v>
+        <v>1.694974350084404</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Thucydides</t>
+          <t>Cellini</t>
         </is>
       </c>
       <c r="B85">
-        <v>1.763670693622397</v>
+        <v>1.675964653078269</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Copernicus</t>
+          <t>William Harrison</t>
         </is>
       </c>
       <c r="B86">
-        <v>1.751372319018221</v>
+        <v>1.658882382102686</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Lujo Brentano</t>
+          <t>Hippolyte Taine</t>
         </is>
       </c>
       <c r="B87">
-        <v>1.743039367653982</v>
+        <v>1.64087536888999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Thomas Mann</t>
+          <t>Molière</t>
         </is>
       </c>
       <c r="B88">
-        <v>1.703900073002881</v>
+        <v>1.636667888280059</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>John Locke</t>
+          <t>Friedrich Schiller</t>
         </is>
       </c>
       <c r="B89">
-        <v>1.699338559217571</v>
+        <v>1.628812937862231</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Frege</t>
+          <t>Walter Raleigh</t>
         </is>
       </c>
       <c r="B90">
-        <v>1.692121581666529</v>
+        <v>1.623401112672756</v>
       </c>
     </row>
     <row r="91">
@@ -8161,277 +8161,277 @@
         </is>
       </c>
       <c r="B91">
-        <v>1.684846334753131</v>
+        <v>1.622660179002237</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>William Harrison</t>
+          <t>Lujo Brentano</t>
         </is>
       </c>
       <c r="B92">
-        <v>1.648909348078887</v>
+        <v>1.615796169156311</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Virgil</t>
+          <t>Edmund Burke</t>
         </is>
       </c>
       <c r="B93">
-        <v>1.641213113647112</v>
+        <v>1.59864287458071</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Walter Raleigh</t>
+          <t>Eduard Zeller</t>
         </is>
       </c>
       <c r="B94">
-        <v>1.638839787840231</v>
+        <v>1.576131858847183</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Durkheim</t>
+          <t>Plato</t>
         </is>
       </c>
       <c r="B95">
-        <v>1.630375015088418</v>
+        <v>1.571562932203727</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Schmoller</t>
+          <t>Montaigne</t>
         </is>
       </c>
       <c r="B96">
-        <v>1.626346487280643</v>
+        <v>1.568249357115401</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Montaigne</t>
+          <t>Dryden</t>
         </is>
       </c>
       <c r="B97">
-        <v>1.62087298728253</v>
+        <v>1.556998362413552</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Karl Mannheim</t>
+          <t>Copernicus</t>
         </is>
       </c>
       <c r="B98">
-        <v>1.611447621794131</v>
+        <v>1.553804143818053</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Hippolyte Taine</t>
+          <t>James Fitzjames Stephen</t>
         </is>
       </c>
       <c r="B99">
-        <v>1.596343330676844</v>
+        <v>1.547911950698299</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Hippocrates</t>
+          <t>John Locke</t>
         </is>
       </c>
       <c r="B100">
-        <v>1.585781190317461</v>
+        <v>1.542623120763105</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cellini</t>
+          <t>Dante Alighieri</t>
         </is>
       </c>
       <c r="B101">
-        <v>1.573723087642146</v>
+        <v>1.525701570528004</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Carl Friedrich</t>
+          <t>Durkheim</t>
         </is>
       </c>
       <c r="B102">
-        <v>1.572190742851307</v>
+        <v>1.520749113056191</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Dante Alighieri</t>
+          <t>Henry George</t>
         </is>
       </c>
       <c r="B103">
-        <v>1.563978096234357</v>
+        <v>1.508175555786881</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Plato</t>
+          <t>Edmund Spenser</t>
         </is>
       </c>
       <c r="B104">
-        <v>1.549361552231368</v>
+        <v>1.497728599098681</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bentham</t>
+          <t>Rilke</t>
         </is>
       </c>
       <c r="B105">
-        <v>1.532754451967845</v>
+        <v>1.480469119555077</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Malthus</t>
+          <t>Bastiat</t>
         </is>
       </c>
       <c r="B106">
-        <v>1.514346657208432</v>
+        <v>1.467834830557547</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Raymond Aron</t>
+          <t>Isaiah Berlin</t>
         </is>
       </c>
       <c r="B107">
-        <v>1.512717738158084</v>
+        <v>1.44086418940796</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Malory</t>
+          <t>Bernard Bolzano</t>
         </is>
       </c>
       <c r="B108">
-        <v>1.508609460730972</v>
+        <v>1.437424374899034</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Thomas Jefferson</t>
+          <t>Aristophanes</t>
         </is>
       </c>
       <c r="B109">
-        <v>1.503564961541606</v>
+        <v>1.426305002709613</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Bastiat</t>
+          <t>Thomas Carlyle</t>
         </is>
       </c>
       <c r="B110">
-        <v>1.464088274944947</v>
+        <v>1.39812315644075</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Friedrich Schiller</t>
+          <t>Adam Smith</t>
         </is>
       </c>
       <c r="B111">
-        <v>1.462386714299289</v>
+        <v>1.386307470049279</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Thomas Carlyle</t>
+          <t>John Stuart Mill</t>
         </is>
       </c>
       <c r="B112">
-        <v>1.398279537415985</v>
+        <v>1.369572121660011</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Robert Owen</t>
+          <t>Bentham</t>
         </is>
       </c>
       <c r="B113">
-        <v>1.380651581621589</v>
+        <v>1.367935567132487</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>William Wordsworth</t>
+          <t>Barthold Georg Niebuhr</t>
         </is>
       </c>
       <c r="B114">
-        <v>1.379738270398923</v>
+        <v>1.349866548748907</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Isaiah Berlin</t>
+          <t>Carl Friedrich</t>
         </is>
       </c>
       <c r="B115">
-        <v>1.379518938962013</v>
+        <v>1.342979344419867</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Bernard Bolzano</t>
+          <t>Karl Mannheim</t>
         </is>
       </c>
       <c r="B116">
-        <v>1.378127997039945</v>
+        <v>1.335223730244476</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Barthold Georg Niebuhr</t>
+          <t>Benjamin Constant</t>
         </is>
       </c>
       <c r="B117">
-        <v>1.356455656757935</v>
+        <v>1.328374719370081</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Benjamin Constant</t>
+          <t>Talcott Parsons</t>
         </is>
       </c>
       <c r="B118">
-        <v>1.341192728078842</v>
+        <v>1.323034650178749</v>
       </c>
     </row>
     <row r="119">
@@ -8441,187 +8441,187 @@
         </is>
       </c>
       <c r="B119">
-        <v>1.331459943486342</v>
+        <v>1.321699294053665</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Dostoyevsky</t>
+          <t>Malory</t>
         </is>
       </c>
       <c r="B120">
-        <v>1.31872978598362</v>
+        <v>1.289394646541084</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Jonathan Swift</t>
+          <t>Archibald Geikie</t>
         </is>
       </c>
       <c r="B121">
-        <v>1.313054083161624</v>
+        <v>1.288085075076891</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Archibald Geikie</t>
+          <t>Robert Owen</t>
         </is>
       </c>
       <c r="B122">
-        <v>1.29296003788417</v>
+        <v>1.277122884951384</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Hamann</t>
+          <t>Pedro Calderón de la Barca</t>
         </is>
       </c>
       <c r="B123">
-        <v>1.272957340893184</v>
+        <v>1.276726515366263</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Renan</t>
+          <t>Jonathan Swift</t>
         </is>
       </c>
       <c r="B124">
-        <v>1.267317383171756</v>
+        <v>1.272355901991389</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Adam Smith</t>
+          <t>Victor Hugo</t>
         </is>
       </c>
       <c r="B125">
-        <v>1.264648483854343</v>
+        <v>1.262344265654125</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Hermann Lotze</t>
+          <t>Hamann</t>
         </is>
       </c>
       <c r="B126">
-        <v>1.259654258329117</v>
+        <v>1.259780851095134</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ernst Cassirer</t>
+          <t>Schmoller</t>
         </is>
       </c>
       <c r="B127">
-        <v>1.250381659203142</v>
+        <v>1.250397309123368</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Martin Luther</t>
+          <t>Hermann Lotze</t>
         </is>
       </c>
       <c r="B128">
-        <v>1.247995299059301</v>
+        <v>1.245323280461024</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>John Milton</t>
+          <t>Martin Luther</t>
         </is>
       </c>
       <c r="B129">
-        <v>1.240763764737004</v>
+        <v>1.242699626958465</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>John C Calhoun</t>
+          <t>Eduard von Hartmann</t>
         </is>
       </c>
       <c r="B130">
-        <v>1.23573765874697</v>
+        <v>1.223832491831317</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Abraham Lincoln</t>
+          <t>Charles Fourier</t>
         </is>
       </c>
       <c r="B131">
-        <v>1.214419034086394</v>
+        <v>1.223617494227961</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Mazzini</t>
+          <t>Rodbertus</t>
         </is>
       </c>
       <c r="B132">
-        <v>1.191435085190502</v>
+        <v>1.216213917538065</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Pedro Calderón de la Barca</t>
+          <t>John Milton</t>
         </is>
       </c>
       <c r="B133">
-        <v>1.17592036615475</v>
+        <v>1.210567360842479</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ludwig Büchner</t>
+          <t>Mazzini</t>
         </is>
       </c>
       <c r="B134">
-        <v>1.172793699868978</v>
+        <v>1.210284102472701</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sombart</t>
+          <t>Ludwig Büchner</t>
         </is>
       </c>
       <c r="B135">
-        <v>1.172113234568164</v>
+        <v>1.206480186244886</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Rodbertus</t>
+          <t>Herbart</t>
         </is>
       </c>
       <c r="B136">
-        <v>1.170690674054424</v>
+        <v>1.194691739548615</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Francis Pretty</t>
+          <t>Dostoyevsky</t>
         </is>
       </c>
       <c r="B137">
-        <v>1.169876541418388</v>
+        <v>1.194563515071064</v>
       </c>
     </row>
     <row r="138">
@@ -8631,117 +8631,117 @@
         </is>
       </c>
       <c r="B138">
-        <v>1.167488984164043</v>
+        <v>1.190442830227727</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Eduard von Hartmann</t>
+          <t>Nassau Senior</t>
         </is>
       </c>
       <c r="B139">
-        <v>1.151745410079613</v>
+        <v>1.189729861718462</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Scheler</t>
+          <t>Ebbinghaus</t>
         </is>
       </c>
       <c r="B140">
-        <v>1.148659871885385</v>
+        <v>1.184590854736836</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Talcott Parsons</t>
+          <t>Sombart</t>
         </is>
       </c>
       <c r="B141">
-        <v>1.144364396346494</v>
+        <v>1.150430894501187</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Edward Haies</t>
+          <t>Francis Pretty</t>
         </is>
       </c>
       <c r="B142">
-        <v>1.141739890355311</v>
+        <v>1.146179439433892</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Nassau Senior</t>
+          <t>Edward Haies</t>
         </is>
       </c>
       <c r="B143">
-        <v>1.12962833383938</v>
+        <v>1.142625620249624</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Simon Newcomb</t>
+          <t>Edward Jenner</t>
         </is>
       </c>
       <c r="B144">
-        <v>1.128908135345951</v>
+        <v>1.125250170468223</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Pasteur</t>
+          <t>Simon Newcomb</t>
         </is>
       </c>
       <c r="B145">
-        <v>1.128132119666461</v>
+        <v>1.125110911493144</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Edward Jenner</t>
+          <t>Scheler</t>
         </is>
       </c>
       <c r="B146">
-        <v>1.117065240139293</v>
+        <v>1.124917930549395</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pericles</t>
+          <t>John Bunyan</t>
         </is>
       </c>
       <c r="B147">
-        <v>1.114937891875815</v>
+        <v>1.104105702276991</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Aesop</t>
+          <t>Pericles</t>
         </is>
       </c>
       <c r="B148">
-        <v>1.101495556720504</v>
+        <v>1.100297905954039</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ebbinghaus</t>
+          <t>Sismondi</t>
         </is>
       </c>
       <c r="B149">
-        <v>1.093142822471142</v>
+        <v>1.088079856628874</v>
       </c>
     </row>
     <row r="150">
@@ -8751,267 +8751,267 @@
         </is>
       </c>
       <c r="B150">
-        <v>1.07094602965666</v>
+        <v>1.070442760106512</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Karl Jaspers</t>
+          <t>Pasteur</t>
         </is>
       </c>
       <c r="B151">
-        <v>1.058966612955772</v>
+        <v>1.066766201348581</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Cervantes</t>
+          <t>Lord Byron</t>
         </is>
       </c>
       <c r="B152">
-        <v>1.035436758454089</v>
+        <v>1.035988091364968</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Froissart</t>
+          <t>Wilhelm von Humboldt</t>
         </is>
       </c>
       <c r="B153">
-        <v>1.033969100069525</v>
+        <v>1.034826073752311</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Francis Bacon</t>
+          <t>Cervantes</t>
         </is>
       </c>
       <c r="B154">
-        <v>1.023436536144467</v>
+        <v>1.031532063935006</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Samuel Johnson</t>
+          <t>Otto Pfleiderer</t>
         </is>
       </c>
       <c r="B155">
-        <v>1.012509110297324</v>
+        <v>1.027003439797117</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>William Caxton</t>
+          <t>Ernst Cassirer</t>
         </is>
       </c>
       <c r="B156">
-        <v>1.004316286410582</v>
+        <v>1.010924742532236</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Robert Burns</t>
+          <t>Herder</t>
         </is>
       </c>
       <c r="B157">
-        <v>1.000155377100815</v>
+        <v>1.009350046250375</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Herder</t>
+          <t>Samuel Johnson</t>
         </is>
       </c>
       <c r="B158">
-        <v>0.9995020731244726</v>
+        <v>1.000595221376581</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Lord Byron</t>
+          <t>Robert Merton</t>
         </is>
       </c>
       <c r="B159">
-        <v>0.9863988059020524</v>
+        <v>0.9765392741358335</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Robert Merton</t>
+          <t>Heinrich Rickert</t>
         </is>
       </c>
       <c r="B160">
-        <v>0.986217547001795</v>
+        <v>0.965086083963295</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Auguste Comte</t>
+          <t>Thünen</t>
         </is>
       </c>
       <c r="B161">
-        <v>0.9806555487501105</v>
+        <v>0.9569194938464207</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Heinrich Rickert</t>
+          <t>Euripides</t>
         </is>
       </c>
       <c r="B162">
-        <v>0.9714114088087195</v>
+        <v>0.956330738829034</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Joseph Lister</t>
+          <t>Aesop</t>
         </is>
       </c>
       <c r="B163">
-        <v>0.9381585590715522</v>
+        <v>0.9467147827541232</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Edmund Burke</t>
+          <t>Blanqui</t>
         </is>
       </c>
       <c r="B164">
-        <v>0.9257876713645938</v>
+        <v>0.9346880061660949</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Newton</t>
+          <t>Joseph Lister</t>
         </is>
       </c>
       <c r="B165">
-        <v>0.9247779287456861</v>
+        <v>0.9289404763511285</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Thünen</t>
+          <t>Robert Burns</t>
         </is>
       </c>
       <c r="B166">
-        <v>0.9175102101891008</v>
+        <v>0.9235043458357635</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Thoreau</t>
+          <t>Newton</t>
         </is>
       </c>
       <c r="B167">
-        <v>0.9136620347706145</v>
+        <v>0.9232326013865231</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Oscar Wilde</t>
+          <t>Karl Jaspers</t>
         </is>
       </c>
       <c r="B168">
-        <v>0.911665030463602</v>
+        <v>0.9202486017595363</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Montesquieu</t>
+          <t>Dilthey</t>
         </is>
       </c>
       <c r="B169">
-        <v>0.8984391237880772</v>
+        <v>0.9097742312726309</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Dilthey</t>
+          <t>William Caxton</t>
         </is>
       </c>
       <c r="B170">
-        <v>0.8915473663314875</v>
+        <v>0.9047810616551968</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Blanqui</t>
+          <t>Oscar Wilde</t>
         </is>
       </c>
       <c r="B171">
-        <v>0.89041160272897</v>
+        <v>0.8933321939181579</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Otto Pfleiderer</t>
+          <t>Montesquieu</t>
         </is>
       </c>
       <c r="B172">
-        <v>0.8857250807052475</v>
+        <v>0.8906935167751276</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Kropotkin</t>
+          <t>Tacitus</t>
         </is>
       </c>
       <c r="B173">
-        <v>0.8636421890034066</v>
+        <v>0.8591262035215645</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Tacitus</t>
+          <t>Walt Whitman</t>
         </is>
       </c>
       <c r="B174">
-        <v>0.8498818286890584</v>
+        <v>0.838595632972703</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>James Fitzjames Stephen</t>
+          <t>Cicero</t>
         </is>
       </c>
       <c r="B175">
-        <v>0.8485816049076225</v>
+        <v>0.831192764447395</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sismondi</t>
+          <t>Richard Cobden</t>
         </is>
       </c>
       <c r="B176">
-        <v>0.8391263504559605</v>
+        <v>0.8285213630909799</v>
       </c>
     </row>
     <row r="177">
@@ -9021,117 +9021,117 @@
         </is>
       </c>
       <c r="B177">
-        <v>0.8310716577792937</v>
+        <v>0.8259382068069172</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Cicero</t>
+          <t>Auguste Comte</t>
         </is>
       </c>
       <c r="B178">
-        <v>0.8229166404050545</v>
+        <v>0.8252275978231793</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Voltaire</t>
+          <t>Francis Bacon</t>
         </is>
       </c>
       <c r="B179">
-        <v>0.811020541302642</v>
+        <v>0.8179978745337428</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Aristophanes</t>
+          <t>Voltaire</t>
         </is>
       </c>
       <c r="B180">
-        <v>0.7960911375821086</v>
+        <v>0.8104973196675005</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Richard Cobden</t>
+          <t>Sophocles</t>
         </is>
       </c>
       <c r="B181">
-        <v>0.7867105309098161</v>
+        <v>0.8090740522898481</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Friedrich Heinrich Jacobi</t>
+          <t>Kropotkin</t>
         </is>
       </c>
       <c r="B182">
-        <v>0.7860087603890801</v>
+        <v>0.8017688368699375</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sophocles</t>
+          <t>Friedrich Heinrich Jacobi</t>
         </is>
       </c>
       <c r="B183">
-        <v>0.764439021769018</v>
+        <v>0.7957563232386514</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ranke</t>
+          <t>Thoreau</t>
         </is>
       </c>
       <c r="B184">
-        <v>0.7436519261213906</v>
+        <v>0.7817397044719859</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Herbart</t>
+          <t>Herbert Spencer</t>
         </is>
       </c>
       <c r="B185">
-        <v>0.7036568557634295</v>
+        <v>0.7362518898668758</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Arthur Moeller van den Bruck</t>
+          <t>Robert Browning</t>
         </is>
       </c>
       <c r="B186">
-        <v>0.6980206291309008</v>
+        <v>0.7058674846252067</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Percy Bysshe Shelley</t>
+          <t>Thomas Browne</t>
         </is>
       </c>
       <c r="B187">
-        <v>0.6721312145481394</v>
+        <v>0.691678896873375</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Thomas Browne</t>
+          <t>Ranke</t>
         </is>
       </c>
       <c r="B188">
-        <v>0.6691105396387244</v>
+        <v>0.6808825309416485</v>
       </c>
     </row>
     <row r="189">
@@ -9141,175 +9141,175 @@
         </is>
       </c>
       <c r="B189">
-        <v>0.664358289639482</v>
+        <v>0.64342958994027</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Vilfredo Pareto</t>
+          <t>Percy Bysshe Shelley</t>
         </is>
       </c>
       <c r="B190">
-        <v>0.5975034435858536</v>
+        <v>0.6426224639869388</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Friedrich Carl von Savigny</t>
+          <t>Auberon Herbert</t>
         </is>
       </c>
       <c r="B191">
-        <v>0.5784749139302755</v>
+        <v>0.6235329836230691</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Proudhon</t>
+          <t>Vilfredo Pareto</t>
         </is>
       </c>
       <c r="B192">
-        <v>0.5328611369108155</v>
+        <v>0.6005864639176979</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Alexander Hamilton</t>
+          <t>Alessandro Manzoni</t>
         </is>
       </c>
       <c r="B193">
-        <v>0.4947186847521773</v>
+        <v>0.5699503107820099</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Auberon Herbert</t>
+          <t>Friedrich Carl von Savigny</t>
         </is>
       </c>
       <c r="B194">
-        <v>0.4784804739715773</v>
+        <v>0.5637306431822932</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Alessandro Manzoni</t>
+          <t>Proudhon</t>
         </is>
       </c>
       <c r="B195">
-        <v>0.4555610095210957</v>
+        <v>0.5315581538501749</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>de Gouges</t>
+          <t>William Godwin</t>
         </is>
       </c>
       <c r="B196">
-        <v>0.4541676193291861</v>
+        <v>0.4666226898247775</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Bigges</t>
+          <t>de Gouges</t>
         </is>
       </c>
       <c r="B197">
-        <v>0.4453205144521945</v>
+        <v>0.4529242366404183</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>William Godwin</t>
+          <t>Bigges</t>
         </is>
       </c>
       <c r="B198">
-        <v>0.4421701077149134</v>
+        <v>0.4431132055422802</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>John Woolman</t>
+          <t>Goethe</t>
         </is>
       </c>
       <c r="B199">
-        <v>0.4244667557424713</v>
+        <v>0.4224428140518977</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Goethe</t>
+          <t>John Woolman</t>
         </is>
       </c>
       <c r="B200">
-        <v>0.4223718143631711</v>
+        <v>0.3779998853560728</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Robert Browning</t>
+          <t>Bakunin</t>
         </is>
       </c>
       <c r="B201">
-        <v>0.2985206288892685</v>
+        <v>0.338955371815804</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Bakunin</t>
+          <t>Alexander Hamilton</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Dryden</t>
+          <t>Froissart</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Edmund Spenser</t>
+          <t>Hippocrates</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Euripides</t>
+          <t>Hölderlin</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Herbert Spencer</t>
+          <t>Lord Acton</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Lord Acton</t>
+          <t>Malthus</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Marcus Aurelius</t>
+          <t>Marlowe</t>
         </is>
       </c>
     </row>
@@ -9323,7 +9323,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Rilke</t>
+          <t>Renan</t>
         </is>
       </c>
     </row>
@@ -9337,14 +9337,14 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Tocqueville</t>
+          <t>Thomas Jefferson</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Walt Whitman</t>
+          <t>William Wordsworth</t>
         </is>
       </c>
     </row>
